--- a/reports/telegram/aegis_daily_2026-08-01.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-01.xlsx
@@ -784,20 +784,44 @@
       <c r="M2" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="N2" s="4" t="inlineStr"/>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O2" s="4" t="n">
         <v>2452.2</v>
       </c>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr"/>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="4" t="inlineStr"/>
-      <c r="Y2" s="4" t="inlineStr"/>
+      <c r="P2" s="4" t="n">
+        <v>2452.2</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>2427.68</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>2476.72</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>2329.59</v>
+      </c>
+      <c r="T2" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U2" s="4" t="n">
+        <v>2648.38</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>2820.03</v>
+      </c>
+      <c r="X2" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y2" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z2" s="4" t="inlineStr"/>
       <c r="AA2" s="4" t="inlineStr"/>
       <c r="AB2" s="4" t="inlineStr">
@@ -815,7 +839,9 @@
       <c r="AF2" s="4" t="inlineStr"/>
       <c r="AG2" s="4" t="inlineStr"/>
       <c r="AH2" s="4" t="inlineStr"/>
-      <c r="AI2" s="4" t="inlineStr"/>
+      <c r="AI2" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ2" s="4" t="inlineStr"/>
       <c r="AK2" s="4" t="inlineStr"/>
       <c r="AL2" s="4" t="inlineStr"/>
@@ -824,7 +850,7 @@
       <c r="AO2" s="4" t="inlineStr"/>
       <c r="AP2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -882,20 +908,44 @@
       <c r="M3" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N3" s="4" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O3" s="4" t="n">
         <v>5196.6</v>
       </c>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="inlineStr"/>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr"/>
-      <c r="Y3" s="4" t="inlineStr"/>
+      <c r="P3" s="4" t="n">
+        <v>5196.6</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>5144.63</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>5248.57</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>4936.77</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>5612.33</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>5976.09</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z3" s="4" t="inlineStr"/>
       <c r="AA3" s="4" t="inlineStr"/>
       <c r="AB3" s="4" t="inlineStr">
@@ -913,7 +963,9 @@
       <c r="AF3" s="4" t="inlineStr"/>
       <c r="AG3" s="4" t="inlineStr"/>
       <c r="AH3" s="4" t="inlineStr"/>
-      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ3" s="4" t="inlineStr"/>
       <c r="AK3" s="4" t="inlineStr"/>
       <c r="AL3" s="4" t="inlineStr"/>
@@ -922,7 +974,7 @@
       <c r="AO3" s="4" t="inlineStr"/>
       <c r="AP3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -976,20 +1028,44 @@
       <c r="M4" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O4" s="4" t="n">
         <v>133.14</v>
       </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="inlineStr"/>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr"/>
-      <c r="Y4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="n">
+        <v>133.14</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>131.81</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>134.47</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>126.48</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>143.79</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>153.11</v>
+      </c>
+      <c r="X4" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z4" s="4" t="inlineStr"/>
       <c r="AA4" s="4" t="inlineStr"/>
       <c r="AB4" s="4" t="inlineStr">
@@ -1007,7 +1083,9 @@
       <c r="AF4" s="4" t="inlineStr"/>
       <c r="AG4" s="4" t="inlineStr"/>
       <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ4" s="4" t="inlineStr"/>
       <c r="AK4" s="4" t="inlineStr"/>
       <c r="AL4" s="4" t="inlineStr"/>
@@ -1016,7 +1094,7 @@
       <c r="AO4" s="4" t="inlineStr"/>
       <c r="AP4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1070,20 +1148,44 @@
       <c r="M5" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O5" s="4" t="n">
         <v>5524</v>
       </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr"/>
-      <c r="Y5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="n">
+        <v>5524</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>5468.76</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>5579.24</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>5247.8</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>5965.92</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>6352.6</v>
+      </c>
+      <c r="X5" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z5" s="4" t="inlineStr"/>
       <c r="AA5" s="4" t="inlineStr"/>
       <c r="AB5" s="4" t="inlineStr">
@@ -1101,7 +1203,9 @@
       <c r="AF5" s="4" t="inlineStr"/>
       <c r="AG5" s="4" t="inlineStr"/>
       <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ5" s="4" t="inlineStr"/>
       <c r="AK5" s="4" t="inlineStr"/>
       <c r="AL5" s="4" t="inlineStr"/>
@@ -1110,7 +1214,7 @@
       <c r="AO5" s="4" t="inlineStr"/>
       <c r="AP5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1168,20 +1272,44 @@
       <c r="M6" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O6" s="4" t="n">
         <v>1346.6</v>
       </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="inlineStr"/>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr"/>
-      <c r="Y6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="n">
+        <v>1346.6</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>1333.13</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>1360.07</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>1279.27</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>1454.33</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>1548.59</v>
+      </c>
+      <c r="X6" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z6" s="4" t="inlineStr"/>
       <c r="AA6" s="4" t="inlineStr"/>
       <c r="AB6" s="4" t="inlineStr">
@@ -1199,7 +1327,9 @@
       <c r="AF6" s="4" t="inlineStr"/>
       <c r="AG6" s="4" t="inlineStr"/>
       <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ6" s="4" t="inlineStr"/>
       <c r="AK6" s="4" t="inlineStr"/>
       <c r="AL6" s="4" t="inlineStr"/>
@@ -1208,7 +1338,7 @@
       <c r="AO6" s="4" t="inlineStr"/>
       <c r="AP6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1262,20 +1392,44 @@
       <c r="M7" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N7" s="4" t="inlineStr"/>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O7" s="4" t="n">
         <v>11602</v>
       </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="inlineStr"/>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr"/>
-      <c r="Y7" s="4" t="inlineStr"/>
+      <c r="P7" s="4" t="n">
+        <v>11602</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>11485.98</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>11718.02</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>11021.9</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>12530.16</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W7" s="4" t="n">
+        <v>13342.3</v>
+      </c>
+      <c r="X7" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y7" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z7" s="4" t="inlineStr"/>
       <c r="AA7" s="4" t="inlineStr"/>
       <c r="AB7" s="4" t="inlineStr">
@@ -1293,7 +1447,9 @@
       <c r="AF7" s="4" t="inlineStr"/>
       <c r="AG7" s="4" t="inlineStr"/>
       <c r="AH7" s="4" t="inlineStr"/>
-      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ7" s="4" t="inlineStr"/>
       <c r="AK7" s="4" t="inlineStr"/>
       <c r="AL7" s="4" t="inlineStr"/>
@@ -1302,7 +1458,7 @@
       <c r="AO7" s="4" t="inlineStr"/>
       <c r="AP7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1356,20 +1512,44 @@
       <c r="M8" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O8" s="4" t="n">
         <v>1158</v>
       </c>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="inlineStr"/>
-      <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="n">
+        <v>1158</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>1146.42</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>1169.58</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>1100.1</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>1250.64</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W8" s="4" t="n">
+        <v>1331.7</v>
+      </c>
+      <c r="X8" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y8" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z8" s="4" t="inlineStr"/>
       <c r="AA8" s="4" t="inlineStr"/>
       <c r="AB8" s="4" t="inlineStr">
@@ -1387,7 +1567,9 @@
       <c r="AF8" s="4" t="inlineStr"/>
       <c r="AG8" s="4" t="inlineStr"/>
       <c r="AH8" s="4" t="inlineStr"/>
-      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ8" s="4" t="inlineStr"/>
       <c r="AK8" s="4" t="inlineStr"/>
       <c r="AL8" s="4" t="inlineStr"/>
@@ -1396,7 +1578,7 @@
       <c r="AO8" s="4" t="inlineStr"/>
       <c r="AP8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1454,20 +1636,44 @@
       <c r="M9" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N9" s="4" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O9" s="4" t="n">
         <v>449.35</v>
       </c>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="inlineStr"/>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr"/>
-      <c r="Y9" s="4" t="inlineStr"/>
+      <c r="P9" s="4" t="n">
+        <v>449.35</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>444.86</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>453.84</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>426.88</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>485.3</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W9" s="4" t="n">
+        <v>516.75</v>
+      </c>
+      <c r="X9" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y9" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z9" s="4" t="inlineStr"/>
       <c r="AA9" s="4" t="inlineStr"/>
       <c r="AB9" s="4" t="inlineStr">
@@ -1485,7 +1691,9 @@
       <c r="AF9" s="4" t="inlineStr"/>
       <c r="AG9" s="4" t="inlineStr"/>
       <c r="AH9" s="4" t="inlineStr"/>
-      <c r="AI9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ9" s="4" t="inlineStr"/>
       <c r="AK9" s="4" t="inlineStr"/>
       <c r="AL9" s="4" t="inlineStr"/>
@@ -1494,7 +1702,7 @@
       <c r="AO9" s="4" t="inlineStr"/>
       <c r="AP9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1552,20 +1760,44 @@
       <c r="M10" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="N10" s="4" t="inlineStr"/>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O10" s="4" t="n">
         <v>287.2</v>
       </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr"/>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="inlineStr"/>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr"/>
-      <c r="Y10" s="4" t="inlineStr"/>
+      <c r="P10" s="4" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>284.33</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>290.07</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>272.84</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>310.18</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W10" s="4" t="n">
+        <v>330.28</v>
+      </c>
+      <c r="X10" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y10" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z10" s="4" t="inlineStr"/>
       <c r="AA10" s="4" t="inlineStr"/>
       <c r="AB10" s="4" t="inlineStr">
@@ -1583,7 +1815,9 @@
       <c r="AF10" s="4" t="inlineStr"/>
       <c r="AG10" s="4" t="inlineStr"/>
       <c r="AH10" s="4" t="inlineStr"/>
-      <c r="AI10" s="4" t="inlineStr"/>
+      <c r="AI10" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ10" s="4" t="inlineStr"/>
       <c r="AK10" s="4" t="inlineStr"/>
       <c r="AL10" s="4" t="inlineStr"/>
@@ -1592,7 +1826,7 @@
       <c r="AO10" s="4" t="inlineStr"/>
       <c r="AP10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1646,20 +1880,44 @@
       <c r="M11" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N11" s="4" t="inlineStr"/>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O11" s="4" t="n">
         <v>10880</v>
       </c>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr"/>
-      <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="inlineStr"/>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr"/>
-      <c r="Y11" s="4" t="inlineStr"/>
+      <c r="P11" s="4" t="n">
+        <v>10880</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>10771.2</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>10988.8</v>
+      </c>
+      <c r="S11" s="4" t="n">
+        <v>10336</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>11750.4</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W11" s="4" t="n">
+        <v>12512</v>
+      </c>
+      <c r="X11" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y11" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z11" s="4" t="inlineStr"/>
       <c r="AA11" s="4" t="inlineStr"/>
       <c r="AB11" s="4" t="inlineStr">
@@ -1677,7 +1935,9 @@
       <c r="AF11" s="4" t="inlineStr"/>
       <c r="AG11" s="4" t="inlineStr"/>
       <c r="AH11" s="4" t="inlineStr"/>
-      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ11" s="4" t="inlineStr"/>
       <c r="AK11" s="4" t="inlineStr"/>
       <c r="AL11" s="4" t="inlineStr"/>
@@ -1686,7 +1946,7 @@
       <c r="AO11" s="4" t="inlineStr"/>
       <c r="AP11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1744,20 +2004,44 @@
       <c r="M12" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="N12" s="4" t="inlineStr"/>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O12" s="4" t="n">
         <v>952.55</v>
       </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr"/>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="inlineStr"/>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr"/>
-      <c r="Y12" s="4" t="inlineStr"/>
+      <c r="P12" s="4" t="n">
+        <v>952.55</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>943.02</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>962.08</v>
+      </c>
+      <c r="S12" s="4" t="n">
+        <v>904.92</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>1028.75</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W12" s="4" t="n">
+        <v>1095.43</v>
+      </c>
+      <c r="X12" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y12" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z12" s="4" t="inlineStr"/>
       <c r="AA12" s="4" t="inlineStr"/>
       <c r="AB12" s="4" t="inlineStr">
@@ -1775,7 +2059,9 @@
       <c r="AF12" s="4" t="inlineStr"/>
       <c r="AG12" s="4" t="inlineStr"/>
       <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="inlineStr"/>
+      <c r="AI12" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ12" s="4" t="inlineStr"/>
       <c r="AK12" s="4" t="inlineStr"/>
       <c r="AL12" s="4" t="inlineStr"/>
@@ -1784,7 +2070,7 @@
       <c r="AO12" s="4" t="inlineStr"/>
       <c r="AP12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1842,20 +2128,44 @@
       <c r="M13" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="4" t="inlineStr"/>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O13" s="4" t="n">
         <v>431.4</v>
       </c>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr"/>
-      <c r="R13" s="4" t="inlineStr"/>
-      <c r="S13" s="4" t="inlineStr"/>
-      <c r="T13" s="4" t="inlineStr"/>
-      <c r="U13" s="4" t="inlineStr"/>
-      <c r="V13" s="4" t="inlineStr"/>
-      <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="4" t="inlineStr"/>
-      <c r="Y13" s="4" t="inlineStr"/>
+      <c r="P13" s="4" t="n">
+        <v>431.4</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>427.09</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>435.71</v>
+      </c>
+      <c r="S13" s="4" t="n">
+        <v>409.83</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>465.91</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W13" s="4" t="n">
+        <v>496.11</v>
+      </c>
+      <c r="X13" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y13" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z13" s="4" t="inlineStr"/>
       <c r="AA13" s="4" t="inlineStr"/>
       <c r="AB13" s="4" t="inlineStr">
@@ -1873,7 +2183,9 @@
       <c r="AF13" s="4" t="inlineStr"/>
       <c r="AG13" s="4" t="inlineStr"/>
       <c r="AH13" s="4" t="inlineStr"/>
-      <c r="AI13" s="4" t="inlineStr"/>
+      <c r="AI13" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ13" s="4" t="inlineStr"/>
       <c r="AK13" s="4" t="inlineStr"/>
       <c r="AL13" s="4" t="inlineStr"/>
@@ -1882,7 +2194,7 @@
       <c r="AO13" s="4" t="inlineStr"/>
       <c r="AP13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1936,20 +2248,44 @@
       <c r="M14" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N14" s="4" t="inlineStr"/>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O14" s="4" t="n">
         <v>2157.8</v>
       </c>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr"/>
-      <c r="S14" s="4" t="inlineStr"/>
-      <c r="T14" s="4" t="inlineStr"/>
-      <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="inlineStr"/>
-      <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="4" t="inlineStr"/>
-      <c r="Y14" s="4" t="inlineStr"/>
+      <c r="P14" s="4" t="n">
+        <v>2157.8</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>2136.22</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>2179.38</v>
+      </c>
+      <c r="S14" s="4" t="n">
+        <v>2049.91</v>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U14" s="4" t="n">
+        <v>2330.42</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W14" s="4" t="n">
+        <v>2481.47</v>
+      </c>
+      <c r="X14" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y14" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z14" s="4" t="inlineStr"/>
       <c r="AA14" s="4" t="inlineStr"/>
       <c r="AB14" s="4" t="inlineStr">
@@ -1967,7 +2303,9 @@
       <c r="AF14" s="4" t="inlineStr"/>
       <c r="AG14" s="4" t="inlineStr"/>
       <c r="AH14" s="4" t="inlineStr"/>
-      <c r="AI14" s="4" t="inlineStr"/>
+      <c r="AI14" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ14" s="4" t="inlineStr"/>
       <c r="AK14" s="4" t="inlineStr"/>
       <c r="AL14" s="4" t="inlineStr"/>
@@ -1976,7 +2314,7 @@
       <c r="AO14" s="4" t="inlineStr"/>
       <c r="AP14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2034,20 +2372,44 @@
       <c r="M15" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="N15" s="4" t="inlineStr"/>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O15" s="4" t="n">
         <v>547.4</v>
       </c>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr"/>
-      <c r="R15" s="4" t="inlineStr"/>
-      <c r="S15" s="4" t="inlineStr"/>
-      <c r="T15" s="4" t="inlineStr"/>
-      <c r="U15" s="4" t="inlineStr"/>
-      <c r="V15" s="4" t="inlineStr"/>
-      <c r="W15" s="4" t="inlineStr"/>
-      <c r="X15" s="4" t="inlineStr"/>
-      <c r="Y15" s="4" t="inlineStr"/>
+      <c r="P15" s="4" t="n">
+        <v>547.4</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>541.9299999999999</v>
+      </c>
+      <c r="R15" s="4" t="n">
+        <v>552.87</v>
+      </c>
+      <c r="S15" s="4" t="n">
+        <v>520.03</v>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U15" s="4" t="n">
+        <v>591.1900000000001</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W15" s="4" t="n">
+        <v>629.51</v>
+      </c>
+      <c r="X15" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y15" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z15" s="4" t="inlineStr"/>
       <c r="AA15" s="4" t="inlineStr"/>
       <c r="AB15" s="4" t="inlineStr">
@@ -2065,7 +2427,9 @@
       <c r="AF15" s="4" t="inlineStr"/>
       <c r="AG15" s="4" t="inlineStr"/>
       <c r="AH15" s="4" t="inlineStr"/>
-      <c r="AI15" s="4" t="inlineStr"/>
+      <c r="AI15" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ15" s="4" t="inlineStr"/>
       <c r="AK15" s="4" t="inlineStr"/>
       <c r="AL15" s="4" t="inlineStr"/>
@@ -2074,7 +2438,7 @@
       <c r="AO15" s="4" t="inlineStr"/>
       <c r="AP15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2128,20 +2492,44 @@
       <c r="M16" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N16" s="4" t="inlineStr"/>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O16" s="4" t="n">
         <v>1363</v>
       </c>
-      <c r="P16" s="4" t="inlineStr"/>
-      <c r="Q16" s="4" t="inlineStr"/>
-      <c r="R16" s="4" t="inlineStr"/>
-      <c r="S16" s="4" t="inlineStr"/>
-      <c r="T16" s="4" t="inlineStr"/>
-      <c r="U16" s="4" t="inlineStr"/>
-      <c r="V16" s="4" t="inlineStr"/>
-      <c r="W16" s="4" t="inlineStr"/>
-      <c r="X16" s="4" t="inlineStr"/>
-      <c r="Y16" s="4" t="inlineStr"/>
+      <c r="P16" s="4" t="n">
+        <v>1363</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>1349.37</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>1376.63</v>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>1294.85</v>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U16" s="4" t="n">
+        <v>1472.04</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W16" s="4" t="n">
+        <v>1567.45</v>
+      </c>
+      <c r="X16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z16" s="4" t="inlineStr"/>
       <c r="AA16" s="4" t="inlineStr"/>
       <c r="AB16" s="4" t="inlineStr">
@@ -2159,7 +2547,9 @@
       <c r="AF16" s="4" t="inlineStr"/>
       <c r="AG16" s="4" t="inlineStr"/>
       <c r="AH16" s="4" t="inlineStr"/>
-      <c r="AI16" s="4" t="inlineStr"/>
+      <c r="AI16" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ16" s="4" t="inlineStr"/>
       <c r="AK16" s="4" t="inlineStr"/>
       <c r="AL16" s="4" t="inlineStr"/>
@@ -2168,7 +2558,7 @@
       <c r="AO16" s="4" t="inlineStr"/>
       <c r="AP16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2222,13 +2612,23 @@
       <c r="M17" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N17" s="4" t="inlineStr"/>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O17" s="4" t="n">
         <v>1438.5</v>
       </c>
-      <c r="P17" s="4" t="inlineStr"/>
-      <c r="Q17" s="4" t="inlineStr"/>
-      <c r="R17" s="4" t="inlineStr"/>
+      <c r="P17" s="4" t="n">
+        <v>1438.5</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>1424.12</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>1452.88</v>
+      </c>
       <c r="S17" s="4" t="n">
         <v>1366.575</v>
       </c>
@@ -2247,7 +2647,9 @@
       <c r="X17" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y17" s="4" t="inlineStr"/>
+      <c r="Y17" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z17" s="4" t="inlineStr"/>
       <c r="AA17" s="4" t="inlineStr"/>
       <c r="AB17" s="4" t="inlineStr">
@@ -2276,7 +2678,7 @@
       <c r="AO17" s="4" t="inlineStr"/>
       <c r="AP17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2330,13 +2732,23 @@
       <c r="M18" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N18" s="4" t="inlineStr"/>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O18" s="4" t="n">
         <v>2014.8</v>
       </c>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr"/>
-      <c r="R18" s="4" t="inlineStr"/>
+      <c r="P18" s="4" t="n">
+        <v>2014.8</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>1994.65</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>2034.95</v>
+      </c>
       <c r="S18" s="4" t="n">
         <v>1914.06</v>
       </c>
@@ -2355,7 +2767,9 @@
       <c r="X18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y18" s="4" t="inlineStr"/>
+      <c r="Y18" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z18" s="4" t="inlineStr"/>
       <c r="AA18" s="4" t="inlineStr"/>
       <c r="AB18" s="4" t="inlineStr">
@@ -2384,7 +2798,7 @@
       <c r="AO18" s="4" t="inlineStr"/>
       <c r="AP18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2438,13 +2852,23 @@
       <c r="M19" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O19" s="4" t="n">
         <v>2417</v>
       </c>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr"/>
-      <c r="R19" s="4" t="inlineStr"/>
+      <c r="P19" s="4" t="n">
+        <v>2417</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>2392.83</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>2441.17</v>
+      </c>
       <c r="S19" s="4" t="n">
         <v>2296.15</v>
       </c>
@@ -2463,7 +2887,9 @@
       <c r="X19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y19" s="4" t="inlineStr"/>
+      <c r="Y19" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z19" s="4" t="inlineStr"/>
       <c r="AA19" s="4" t="inlineStr"/>
       <c r="AB19" s="4" t="inlineStr">
@@ -2492,7 +2918,7 @@
       <c r="AO19" s="4" t="inlineStr"/>
       <c r="AP19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2546,13 +2972,23 @@
       <c r="M20" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N20" s="4" t="inlineStr"/>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O20" s="4" t="n">
         <v>1625.5</v>
       </c>
-      <c r="P20" s="4" t="inlineStr"/>
-      <c r="Q20" s="4" t="inlineStr"/>
-      <c r="R20" s="4" t="inlineStr"/>
+      <c r="P20" s="4" t="n">
+        <v>1625.5</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>1609.24</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>1641.76</v>
+      </c>
       <c r="S20" s="4" t="n">
         <v>1544.225</v>
       </c>
@@ -2571,7 +3007,9 @@
       <c r="X20" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y20" s="4" t="inlineStr"/>
+      <c r="Y20" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z20" s="4" t="inlineStr"/>
       <c r="AA20" s="4" t="inlineStr"/>
       <c r="AB20" s="4" t="inlineStr">
@@ -2600,7 +3038,7 @@
       <c r="AO20" s="4" t="inlineStr"/>
       <c r="AP20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2654,13 +3092,23 @@
       <c r="M21" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N21" s="4" t="inlineStr"/>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O21" s="4" t="n">
         <v>345.8</v>
       </c>
-      <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="4" t="inlineStr"/>
-      <c r="R21" s="4" t="inlineStr"/>
+      <c r="P21" s="4" t="n">
+        <v>345.8</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>342.34</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>349.26</v>
+      </c>
       <c r="S21" s="4" t="n">
         <v>328.51</v>
       </c>
@@ -2679,7 +3127,9 @@
       <c r="X21" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y21" s="4" t="inlineStr"/>
+      <c r="Y21" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z21" s="4" t="inlineStr"/>
       <c r="AA21" s="4" t="inlineStr"/>
       <c r="AB21" s="4" t="inlineStr">
@@ -2708,7 +3158,7 @@
       <c r="AO21" s="4" t="inlineStr"/>
       <c r="AP21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2762,13 +3212,23 @@
       <c r="M22" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N22" s="4" t="inlineStr"/>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O22" s="4" t="n">
         <v>389.3</v>
       </c>
-      <c r="P22" s="4" t="inlineStr"/>
-      <c r="Q22" s="4" t="inlineStr"/>
-      <c r="R22" s="4" t="inlineStr"/>
+      <c r="P22" s="4" t="n">
+        <v>389.3</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>385.41</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>393.19</v>
+      </c>
       <c r="S22" s="4" t="n">
         <v>369.835</v>
       </c>
@@ -2787,7 +3247,9 @@
       <c r="X22" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y22" s="4" t="inlineStr"/>
+      <c r="Y22" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z22" s="4" t="inlineStr"/>
       <c r="AA22" s="4" t="inlineStr"/>
       <c r="AB22" s="4" t="inlineStr">
@@ -2816,7 +3278,7 @@
       <c r="AO22" s="4" t="inlineStr"/>
       <c r="AP22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2870,13 +3332,23 @@
       <c r="M23" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N23" s="4" t="inlineStr"/>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O23" s="4" t="n">
         <v>285.9</v>
       </c>
-      <c r="P23" s="4" t="inlineStr"/>
-      <c r="Q23" s="4" t="inlineStr"/>
-      <c r="R23" s="4" t="inlineStr"/>
+      <c r="P23" s="4" t="n">
+        <v>285.9</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>283.04</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>288.76</v>
+      </c>
       <c r="S23" s="4" t="n">
         <v>271.605</v>
       </c>
@@ -2895,7 +3367,9 @@
       <c r="X23" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y23" s="4" t="inlineStr"/>
+      <c r="Y23" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z23" s="4" t="inlineStr"/>
       <c r="AA23" s="4" t="inlineStr"/>
       <c r="AB23" s="4" t="inlineStr">
@@ -2924,7 +3398,7 @@
       <c r="AO23" s="4" t="inlineStr"/>
       <c r="AP23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2978,13 +3452,23 @@
       <c r="M24" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N24" s="4" t="inlineStr"/>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O24" s="4" t="n">
         <v>494.4</v>
       </c>
-      <c r="P24" s="4" t="inlineStr"/>
-      <c r="Q24" s="4" t="inlineStr"/>
-      <c r="R24" s="4" t="inlineStr"/>
+      <c r="P24" s="4" t="n">
+        <v>494.4</v>
+      </c>
+      <c r="Q24" s="4" t="n">
+        <v>489.46</v>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>499.34</v>
+      </c>
       <c r="S24" s="4" t="n">
         <v>469.6799999999999</v>
       </c>
@@ -3003,7 +3487,9 @@
       <c r="X24" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y24" s="4" t="inlineStr"/>
+      <c r="Y24" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z24" s="4" t="inlineStr"/>
       <c r="AA24" s="4" t="inlineStr"/>
       <c r="AB24" s="4" t="inlineStr">
@@ -3032,7 +3518,7 @@
       <c r="AO24" s="4" t="inlineStr"/>
       <c r="AP24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -3086,13 +3572,23 @@
       <c r="M25" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O25" s="4" t="n">
         <v>388.7</v>
       </c>
-      <c r="P25" s="4" t="inlineStr"/>
-      <c r="Q25" s="4" t="inlineStr"/>
-      <c r="R25" s="4" t="inlineStr"/>
+      <c r="P25" s="4" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="Q25" s="4" t="n">
+        <v>384.81</v>
+      </c>
+      <c r="R25" s="4" t="n">
+        <v>392.59</v>
+      </c>
       <c r="S25" s="4" t="n">
         <v>369.265</v>
       </c>
@@ -3111,7 +3607,9 @@
       <c r="X25" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y25" s="4" t="inlineStr"/>
+      <c r="Y25" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z25" s="4" t="inlineStr"/>
       <c r="AA25" s="4" t="inlineStr"/>
       <c r="AB25" s="4" t="inlineStr">
@@ -3140,7 +3638,7 @@
       <c r="AO25" s="4" t="inlineStr"/>
       <c r="AP25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -3194,13 +3692,23 @@
       <c r="M26" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O26" s="4" t="n">
         <v>411.3</v>
       </c>
-      <c r="P26" s="4" t="inlineStr"/>
-      <c r="Q26" s="4" t="inlineStr"/>
-      <c r="R26" s="4" t="inlineStr"/>
+      <c r="P26" s="4" t="n">
+        <v>411.3</v>
+      </c>
+      <c r="Q26" s="4" t="n">
+        <v>407.19</v>
+      </c>
+      <c r="R26" s="4" t="n">
+        <v>415.41</v>
+      </c>
       <c r="S26" s="4" t="n">
         <v>390.735</v>
       </c>
@@ -3219,7 +3727,9 @@
       <c r="X26" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y26" s="4" t="inlineStr"/>
+      <c r="Y26" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z26" s="4" t="inlineStr"/>
       <c r="AA26" s="4" t="inlineStr"/>
       <c r="AB26" s="4" t="inlineStr">
@@ -3248,7 +3758,7 @@
       <c r="AO26" s="4" t="inlineStr"/>
       <c r="AP26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -3298,13 +3808,23 @@
       <c r="M27" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O27" s="4" t="n">
         <v>5406</v>
       </c>
-      <c r="P27" s="4" t="inlineStr"/>
-      <c r="Q27" s="4" t="inlineStr"/>
-      <c r="R27" s="4" t="inlineStr"/>
+      <c r="P27" s="4" t="n">
+        <v>5406</v>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>5351.94</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>5460.06</v>
+      </c>
       <c r="S27" s="4" t="n">
         <v>5135.7</v>
       </c>
@@ -3323,7 +3843,9 @@
       <c r="X27" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y27" s="4" t="inlineStr"/>
+      <c r="Y27" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z27" s="4" t="inlineStr"/>
       <c r="AA27" s="4" t="inlineStr"/>
       <c r="AB27" s="4" t="inlineStr">
@@ -3352,7 +3874,7 @@
       <c r="AO27" s="4" t="inlineStr"/>
       <c r="AP27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -3482,7 +4004,7 @@
       <c r="AO28" s="4" t="inlineStr"/>
       <c r="AP28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -3551,14 +4073,30 @@
       <c r="P29" s="4" t="n">
         <v>358.56</v>
       </c>
-      <c r="Q29" s="4" t="inlineStr"/>
-      <c r="R29" s="4" t="inlineStr"/>
-      <c r="S29" s="4" t="inlineStr"/>
-      <c r="T29" s="4" t="inlineStr"/>
-      <c r="U29" s="4" t="inlineStr"/>
-      <c r="V29" s="4" t="inlineStr"/>
-      <c r="W29" s="4" t="inlineStr"/>
-      <c r="X29" s="4" t="inlineStr"/>
+      <c r="Q29" s="4" t="n">
+        <v>354.97</v>
+      </c>
+      <c r="R29" s="4" t="n">
+        <v>362.15</v>
+      </c>
+      <c r="S29" s="4" t="n">
+        <v>340.63</v>
+      </c>
+      <c r="T29" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>387.24</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W29" s="4" t="n">
+        <v>412.34</v>
+      </c>
+      <c r="X29" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y29" s="4" t="n">
         <v>0</v>
       </c>
@@ -3594,7 +4132,7 @@
       <c r="AO29" s="4" t="inlineStr"/>
       <c r="AP29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -3663,14 +4201,30 @@
       <c r="P30" s="4" t="n">
         <v>202.81</v>
       </c>
-      <c r="Q30" s="4" t="inlineStr"/>
-      <c r="R30" s="4" t="inlineStr"/>
-      <c r="S30" s="4" t="inlineStr"/>
-      <c r="T30" s="4" t="inlineStr"/>
-      <c r="U30" s="4" t="inlineStr"/>
-      <c r="V30" s="4" t="inlineStr"/>
-      <c r="W30" s="4" t="inlineStr"/>
-      <c r="X30" s="4" t="inlineStr"/>
+      <c r="Q30" s="4" t="n">
+        <v>200.78</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>204.84</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>192.67</v>
+      </c>
+      <c r="T30" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>219.03</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W30" s="4" t="n">
+        <v>233.23</v>
+      </c>
+      <c r="X30" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y30" s="4" t="n">
         <v>0</v>
       </c>
@@ -3706,7 +4260,7 @@
       <c r="AO30" s="4" t="inlineStr"/>
       <c r="AP30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -3775,14 +4329,30 @@
       <c r="P31" s="4" t="n">
         <v>341.1</v>
       </c>
-      <c r="Q31" s="4" t="inlineStr"/>
-      <c r="R31" s="4" t="inlineStr"/>
-      <c r="S31" s="4" t="inlineStr"/>
-      <c r="T31" s="4" t="inlineStr"/>
-      <c r="U31" s="4" t="inlineStr"/>
-      <c r="V31" s="4" t="inlineStr"/>
-      <c r="W31" s="4" t="inlineStr"/>
-      <c r="X31" s="4" t="inlineStr"/>
+      <c r="Q31" s="4" t="n">
+        <v>337.69</v>
+      </c>
+      <c r="R31" s="4" t="n">
+        <v>344.51</v>
+      </c>
+      <c r="S31" s="4" t="n">
+        <v>324.05</v>
+      </c>
+      <c r="T31" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U31" s="4" t="n">
+        <v>368.39</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W31" s="4" t="n">
+        <v>392.26</v>
+      </c>
+      <c r="X31" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y31" s="4" t="n">
         <v>0</v>
       </c>
@@ -3818,7 +4388,7 @@
       <c r="AO31" s="4" t="inlineStr"/>
       <c r="AP31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -3887,14 +4457,30 @@
       <c r="P32" s="4" t="n">
         <v>225.02</v>
       </c>
-      <c r="Q32" s="4" t="inlineStr"/>
-      <c r="R32" s="4" t="inlineStr"/>
-      <c r="S32" s="4" t="inlineStr"/>
-      <c r="T32" s="4" t="inlineStr"/>
-      <c r="U32" s="4" t="inlineStr"/>
-      <c r="V32" s="4" t="inlineStr"/>
-      <c r="W32" s="4" t="inlineStr"/>
-      <c r="X32" s="4" t="inlineStr"/>
+      <c r="Q32" s="4" t="n">
+        <v>222.77</v>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="S32" s="4" t="n">
+        <v>213.77</v>
+      </c>
+      <c r="T32" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>243.02</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W32" s="4" t="n">
+        <v>258.77</v>
+      </c>
+      <c r="X32" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y32" s="4" t="n">
         <v>0</v>
       </c>
@@ -3930,7 +4516,7 @@
       <c r="AO32" s="4" t="inlineStr"/>
       <c r="AP32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -3999,14 +4585,30 @@
       <c r="P33" s="4" t="n">
         <v>1065.22</v>
       </c>
-      <c r="Q33" s="4" t="inlineStr"/>
-      <c r="R33" s="4" t="inlineStr"/>
-      <c r="S33" s="4" t="inlineStr"/>
-      <c r="T33" s="4" t="inlineStr"/>
-      <c r="U33" s="4" t="inlineStr"/>
-      <c r="V33" s="4" t="inlineStr"/>
-      <c r="W33" s="4" t="inlineStr"/>
-      <c r="X33" s="4" t="inlineStr"/>
+      <c r="Q33" s="4" t="n">
+        <v>1054.57</v>
+      </c>
+      <c r="R33" s="4" t="n">
+        <v>1075.87</v>
+      </c>
+      <c r="S33" s="4" t="n">
+        <v>1011.96</v>
+      </c>
+      <c r="T33" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U33" s="4" t="n">
+        <v>1150.44</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W33" s="4" t="n">
+        <v>1225</v>
+      </c>
+      <c r="X33" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y33" s="4" t="n">
         <v>0</v>
       </c>
@@ -4042,7 +4644,7 @@
       <c r="AO33" s="4" t="inlineStr"/>
       <c r="AP33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -4111,14 +4713,30 @@
       <c r="P34" s="4" t="n">
         <v>333.74</v>
       </c>
-      <c r="Q34" s="4" t="inlineStr"/>
-      <c r="R34" s="4" t="inlineStr"/>
-      <c r="S34" s="4" t="inlineStr"/>
-      <c r="T34" s="4" t="inlineStr"/>
-      <c r="U34" s="4" t="inlineStr"/>
-      <c r="V34" s="4" t="inlineStr"/>
-      <c r="W34" s="4" t="inlineStr"/>
-      <c r="X34" s="4" t="inlineStr"/>
+      <c r="Q34" s="4" t="n">
+        <v>330.4</v>
+      </c>
+      <c r="R34" s="4" t="n">
+        <v>337.08</v>
+      </c>
+      <c r="S34" s="4" t="n">
+        <v>317.05</v>
+      </c>
+      <c r="T34" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U34" s="4" t="n">
+        <v>360.44</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W34" s="4" t="n">
+        <v>383.8</v>
+      </c>
+      <c r="X34" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y34" s="4" t="n">
         <v>0</v>
       </c>
@@ -4154,7 +4772,7 @@
       <c r="AO34" s="4" t="inlineStr"/>
       <c r="AP34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -4223,14 +4841,30 @@
       <c r="P35" s="4" t="n">
         <v>393.82</v>
       </c>
-      <c r="Q35" s="4" t="inlineStr"/>
-      <c r="R35" s="4" t="inlineStr"/>
-      <c r="S35" s="4" t="inlineStr"/>
-      <c r="T35" s="4" t="inlineStr"/>
-      <c r="U35" s="4" t="inlineStr"/>
-      <c r="V35" s="4" t="inlineStr"/>
-      <c r="W35" s="4" t="inlineStr"/>
-      <c r="X35" s="4" t="inlineStr"/>
+      <c r="Q35" s="4" t="n">
+        <v>389.88</v>
+      </c>
+      <c r="R35" s="4" t="n">
+        <v>397.76</v>
+      </c>
+      <c r="S35" s="4" t="n">
+        <v>374.13</v>
+      </c>
+      <c r="T35" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U35" s="4" t="n">
+        <v>425.33</v>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W35" s="4" t="n">
+        <v>452.89</v>
+      </c>
+      <c r="X35" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y35" s="4" t="n">
         <v>0</v>
       </c>
@@ -4266,7 +4900,7 @@
       <c r="AO35" s="4" t="inlineStr"/>
       <c r="AP35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -4335,14 +4969,30 @@
       <c r="P36" s="4" t="n">
         <v>81.56</v>
       </c>
-      <c r="Q36" s="4" t="inlineStr"/>
-      <c r="R36" s="4" t="inlineStr"/>
-      <c r="S36" s="4" t="inlineStr"/>
-      <c r="T36" s="4" t="inlineStr"/>
-      <c r="U36" s="4" t="inlineStr"/>
-      <c r="V36" s="4" t="inlineStr"/>
-      <c r="W36" s="4" t="inlineStr"/>
-      <c r="X36" s="4" t="inlineStr"/>
+      <c r="Q36" s="4" t="n">
+        <v>80.73999999999999</v>
+      </c>
+      <c r="R36" s="4" t="n">
+        <v>82.38</v>
+      </c>
+      <c r="S36" s="4" t="n">
+        <v>77.48</v>
+      </c>
+      <c r="T36" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U36" s="4" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="W36" s="4" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="X36" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y36" s="4" t="n">
         <v>0</v>
       </c>
@@ -4378,7 +5028,7 @@
       <c r="AO36" s="4" t="inlineStr"/>
       <c r="AP36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -4447,14 +5097,30 @@
       <c r="P37" s="4" t="n">
         <v>159.84</v>
       </c>
-      <c r="Q37" s="4" t="inlineStr"/>
-      <c r="R37" s="4" t="inlineStr"/>
-      <c r="S37" s="4" t="inlineStr"/>
-      <c r="T37" s="4" t="inlineStr"/>
-      <c r="U37" s="4" t="inlineStr"/>
-      <c r="V37" s="4" t="inlineStr"/>
-      <c r="W37" s="4" t="inlineStr"/>
-      <c r="X37" s="4" t="inlineStr"/>
+      <c r="Q37" s="4" t="n">
+        <v>158.24</v>
+      </c>
+      <c r="R37" s="4" t="n">
+        <v>161.44</v>
+      </c>
+      <c r="S37" s="4" t="n">
+        <v>151.85</v>
+      </c>
+      <c r="T37" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U37" s="4" t="n">
+        <v>172.63</v>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W37" s="4" t="n">
+        <v>183.82</v>
+      </c>
+      <c r="X37" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y37" s="4" t="n">
         <v>0</v>
       </c>
@@ -4490,7 +5156,7 @@
       <c r="AO37" s="4" t="inlineStr"/>
       <c r="AP37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -4559,14 +5225,30 @@
       <c r="P38" s="4" t="n">
         <v>95.04000000000001</v>
       </c>
-      <c r="Q38" s="4" t="inlineStr"/>
-      <c r="R38" s="4" t="inlineStr"/>
-      <c r="S38" s="4" t="inlineStr"/>
-      <c r="T38" s="4" t="inlineStr"/>
-      <c r="U38" s="4" t="inlineStr"/>
-      <c r="V38" s="4" t="inlineStr"/>
-      <c r="W38" s="4" t="inlineStr"/>
-      <c r="X38" s="4" t="inlineStr"/>
+      <c r="Q38" s="4" t="n">
+        <v>94.09</v>
+      </c>
+      <c r="R38" s="4" t="n">
+        <v>95.98999999999999</v>
+      </c>
+      <c r="S38" s="4" t="n">
+        <v>90.29000000000001</v>
+      </c>
+      <c r="T38" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U38" s="4" t="n">
+        <v>102.64</v>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W38" s="4" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="X38" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y38" s="4" t="n">
         <v>0</v>
       </c>
@@ -4602,7 +5284,7 @@
       <c r="AO38" s="4" t="inlineStr"/>
       <c r="AP38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -4671,14 +5353,30 @@
       <c r="P39" s="4" t="n">
         <v>214.03</v>
       </c>
-      <c r="Q39" s="4" t="inlineStr"/>
-      <c r="R39" s="4" t="inlineStr"/>
-      <c r="S39" s="4" t="inlineStr"/>
-      <c r="T39" s="4" t="inlineStr"/>
-      <c r="U39" s="4" t="inlineStr"/>
-      <c r="V39" s="4" t="inlineStr"/>
-      <c r="W39" s="4" t="inlineStr"/>
-      <c r="X39" s="4" t="inlineStr"/>
+      <c r="Q39" s="4" t="n">
+        <v>211.89</v>
+      </c>
+      <c r="R39" s="4" t="n">
+        <v>216.17</v>
+      </c>
+      <c r="S39" s="4" t="n">
+        <v>203.33</v>
+      </c>
+      <c r="T39" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U39" s="4" t="n">
+        <v>231.15</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W39" s="4" t="n">
+        <v>246.13</v>
+      </c>
+      <c r="X39" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y39" s="4" t="n">
         <v>0</v>
       </c>
@@ -4714,7 +5412,7 @@
       <c r="AO39" s="4" t="inlineStr"/>
       <c r="AP39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -4783,14 +5481,30 @@
       <c r="P40" s="4" t="n">
         <v>338.87</v>
       </c>
-      <c r="Q40" s="4" t="inlineStr"/>
-      <c r="R40" s="4" t="inlineStr"/>
-      <c r="S40" s="4" t="inlineStr"/>
-      <c r="T40" s="4" t="inlineStr"/>
-      <c r="U40" s="4" t="inlineStr"/>
-      <c r="V40" s="4" t="inlineStr"/>
-      <c r="W40" s="4" t="inlineStr"/>
-      <c r="X40" s="4" t="inlineStr"/>
+      <c r="Q40" s="4" t="n">
+        <v>335.48</v>
+      </c>
+      <c r="R40" s="4" t="n">
+        <v>342.26</v>
+      </c>
+      <c r="S40" s="4" t="n">
+        <v>321.93</v>
+      </c>
+      <c r="T40" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U40" s="4" t="n">
+        <v>365.98</v>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W40" s="4" t="n">
+        <v>389.7</v>
+      </c>
+      <c r="X40" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y40" s="4" t="n">
         <v>0</v>
       </c>
@@ -4826,7 +5540,7 @@
       <c r="AO40" s="4" t="inlineStr"/>
       <c r="AP40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -4895,14 +5609,30 @@
       <c r="P41" s="4" t="n">
         <v>97.67</v>
       </c>
-      <c r="Q41" s="4" t="inlineStr"/>
-      <c r="R41" s="4" t="inlineStr"/>
-      <c r="S41" s="4" t="inlineStr"/>
-      <c r="T41" s="4" t="inlineStr"/>
-      <c r="U41" s="4" t="inlineStr"/>
-      <c r="V41" s="4" t="inlineStr"/>
-      <c r="W41" s="4" t="inlineStr"/>
-      <c r="X41" s="4" t="inlineStr"/>
+      <c r="Q41" s="4" t="n">
+        <v>96.69</v>
+      </c>
+      <c r="R41" s="4" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="S41" s="4" t="n">
+        <v>92.79000000000001</v>
+      </c>
+      <c r="T41" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U41" s="4" t="n">
+        <v>105.48</v>
+      </c>
+      <c r="V41" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W41" s="4" t="n">
+        <v>112.32</v>
+      </c>
+      <c r="X41" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y41" s="4" t="n">
         <v>0</v>
       </c>
@@ -4938,7 +5668,7 @@
       <c r="AO41" s="4" t="inlineStr"/>
       <c r="AP41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -5007,14 +5737,30 @@
       <c r="P42" s="4" t="n">
         <v>267.71</v>
       </c>
-      <c r="Q42" s="4" t="inlineStr"/>
-      <c r="R42" s="4" t="inlineStr"/>
-      <c r="S42" s="4" t="inlineStr"/>
-      <c r="T42" s="4" t="inlineStr"/>
-      <c r="U42" s="4" t="inlineStr"/>
-      <c r="V42" s="4" t="inlineStr"/>
-      <c r="W42" s="4" t="inlineStr"/>
-      <c r="X42" s="4" t="inlineStr"/>
+      <c r="Q42" s="4" t="n">
+        <v>265.03</v>
+      </c>
+      <c r="R42" s="4" t="n">
+        <v>270.39</v>
+      </c>
+      <c r="S42" s="4" t="n">
+        <v>254.32</v>
+      </c>
+      <c r="T42" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U42" s="4" t="n">
+        <v>289.13</v>
+      </c>
+      <c r="V42" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W42" s="4" t="n">
+        <v>307.87</v>
+      </c>
+      <c r="X42" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y42" s="4" t="n">
         <v>0</v>
       </c>
@@ -5050,7 +5796,7 @@
       <c r="AO42" s="4" t="inlineStr"/>
       <c r="AP42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_daily_2026-08-01.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-01.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AP$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AG$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP42"/>
+  <dimension ref="A1:AG42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -502,20 +502,11 @@
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="11" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="22" customWidth="1" min="29" max="29"/>
-    <col width="32" customWidth="1" min="30" max="30"/>
-    <col width="28" customWidth="1" min="31" max="31"/>
-    <col width="20" customWidth="1" min="32" max="32"/>
-    <col width="17" customWidth="1" min="33" max="33"/>
-    <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="17" customWidth="1" min="35" max="35"/>
-    <col width="20" customWidth="1" min="36" max="36"/>
-    <col width="21" customWidth="1" min="37" max="37"/>
-    <col width="12" customWidth="1" min="38" max="38"/>
-    <col width="15" customWidth="1" min="39" max="39"/>
-    <col width="17" customWidth="1" min="40" max="40"/>
-    <col width="18" customWidth="1" min="41" max="41"/>
-    <col width="20" customWidth="1" min="42" max="42"/>
+    <col width="32" customWidth="1" min="29" max="29"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="18" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+    <col width="20" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -661,70 +652,25 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Exit Triggers Hit</t>
+          <t>Top Drivers</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Top Drivers</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Risk Flags</t>
+          <t>Portfolio Weight %</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Expected Alpha %</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Sector Exposure %</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Portfolio Weight %</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Alpha %</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Confidence Band Low %</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Confidence Band High %</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Correlation</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Hist Win Rate %</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Hist Median Ret %</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>Hist Avg Hold (d)</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Last Updated (UTC)</t>
         </is>
@@ -829,28 +775,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC2" s="4" t="inlineStr"/>
-      <c r="AD2" s="4" t="inlineStr">
+      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Ai Hybrid</t>
         </is>
       </c>
+      <c r="AD2" s="4" t="inlineStr"/>
       <c r="AE2" s="4" t="inlineStr"/>
-      <c r="AF2" s="4" t="inlineStr"/>
-      <c r="AG2" s="4" t="inlineStr"/>
-      <c r="AH2" s="4" t="inlineStr"/>
-      <c r="AI2" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ2" s="4" t="inlineStr"/>
-      <c r="AK2" s="4" t="inlineStr"/>
-      <c r="AL2" s="4" t="inlineStr"/>
-      <c r="AM2" s="4" t="inlineStr"/>
-      <c r="AN2" s="4" t="inlineStr"/>
-      <c r="AO2" s="4" t="inlineStr"/>
-      <c r="AP2" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -953,28 +890,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC3" s="4" t="inlineStr"/>
-      <c r="AD3" s="4" t="inlineStr">
+      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · Ai Hybrid</t>
         </is>
       </c>
+      <c r="AD3" s="4" t="inlineStr"/>
       <c r="AE3" s="4" t="inlineStr"/>
-      <c r="AF3" s="4" t="inlineStr"/>
-      <c r="AG3" s="4" t="inlineStr"/>
-      <c r="AH3" s="4" t="inlineStr"/>
-      <c r="AI3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ3" s="4" t="inlineStr"/>
-      <c r="AK3" s="4" t="inlineStr"/>
-      <c r="AL3" s="4" t="inlineStr"/>
-      <c r="AM3" s="4" t="inlineStr"/>
-      <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr"/>
-      <c r="AP3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -1073,28 +1001,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC4" s="4" t="inlineStr"/>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>Quality · Momentum · Ai Hybrid</t>
         </is>
       </c>
+      <c r="AD4" s="4" t="inlineStr"/>
       <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr"/>
-      <c r="AP4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -1193,28 +1112,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC5" s="4" t="inlineStr"/>
-      <c r="AD5" s="4" t="inlineStr">
+      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>Trend · Growth · Value</t>
         </is>
       </c>
+      <c r="AD5" s="4" t="inlineStr"/>
       <c r="AE5" s="4" t="inlineStr"/>
-      <c r="AF5" s="4" t="inlineStr"/>
-      <c r="AG5" s="4" t="inlineStr"/>
-      <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr"/>
-      <c r="AL5" s="4" t="inlineStr"/>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
-      <c r="AP5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -1317,28 +1227,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC6" s="4" t="inlineStr"/>
-      <c r="AD6" s="4" t="inlineStr">
+      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Momentum</t>
         </is>
       </c>
+      <c r="AD6" s="4" t="inlineStr"/>
       <c r="AE6" s="4" t="inlineStr"/>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -1437,28 +1338,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC7" s="4" t="inlineStr"/>
-      <c r="AD7" s="4" t="inlineStr">
+      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · Momentum</t>
         </is>
       </c>
+      <c r="AD7" s="4" t="inlineStr"/>
       <c r="AE7" s="4" t="inlineStr"/>
-      <c r="AF7" s="4" t="inlineStr"/>
-      <c r="AG7" s="4" t="inlineStr"/>
-      <c r="AH7" s="4" t="inlineStr"/>
-      <c r="AI7" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ7" s="4" t="inlineStr"/>
-      <c r="AK7" s="4" t="inlineStr"/>
-      <c r="AL7" s="4" t="inlineStr"/>
-      <c r="AM7" s="4" t="inlineStr"/>
-      <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr"/>
-      <c r="AP7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -1557,28 +1449,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC8" s="4" t="inlineStr"/>
-      <c r="AD8" s="4" t="inlineStr">
+      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>Mean Reversion · Quality · Momentum</t>
         </is>
       </c>
+      <c r="AD8" s="4" t="inlineStr"/>
       <c r="AE8" s="4" t="inlineStr"/>
-      <c r="AF8" s="4" t="inlineStr"/>
-      <c r="AG8" s="4" t="inlineStr"/>
-      <c r="AH8" s="4" t="inlineStr"/>
-      <c r="AI8" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ8" s="4" t="inlineStr"/>
-      <c r="AK8" s="4" t="inlineStr"/>
-      <c r="AL8" s="4" t="inlineStr"/>
-      <c r="AM8" s="4" t="inlineStr"/>
-      <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr"/>
-      <c r="AP8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -1681,28 +1564,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC9" s="4" t="inlineStr"/>
-      <c r="AD9" s="4" t="inlineStr">
+      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>Value · Mean Reversion · Growth</t>
         </is>
       </c>
+      <c r="AD9" s="4" t="inlineStr"/>
       <c r="AE9" s="4" t="inlineStr"/>
-      <c r="AF9" s="4" t="inlineStr"/>
-      <c r="AG9" s="4" t="inlineStr"/>
-      <c r="AH9" s="4" t="inlineStr"/>
-      <c r="AI9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ9" s="4" t="inlineStr"/>
-      <c r="AK9" s="4" t="inlineStr"/>
-      <c r="AL9" s="4" t="inlineStr"/>
-      <c r="AM9" s="4" t="inlineStr"/>
-      <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
-      <c r="AP9" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -1805,28 +1679,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC10" s="4" t="inlineStr"/>
-      <c r="AD10" s="4" t="inlineStr">
+      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Value</t>
         </is>
       </c>
+      <c r="AD10" s="4" t="inlineStr"/>
       <c r="AE10" s="4" t="inlineStr"/>
-      <c r="AF10" s="4" t="inlineStr"/>
-      <c r="AG10" s="4" t="inlineStr"/>
-      <c r="AH10" s="4" t="inlineStr"/>
-      <c r="AI10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ10" s="4" t="inlineStr"/>
-      <c r="AK10" s="4" t="inlineStr"/>
-      <c r="AL10" s="4" t="inlineStr"/>
-      <c r="AM10" s="4" t="inlineStr"/>
-      <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr"/>
-      <c r="AP10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -1925,28 +1790,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC11" s="4" t="inlineStr"/>
-      <c r="AD11" s="4" t="inlineStr">
+      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>Value · Quality · Trend</t>
         </is>
       </c>
+      <c r="AD11" s="4" t="inlineStr"/>
       <c r="AE11" s="4" t="inlineStr"/>
-      <c r="AF11" s="4" t="inlineStr"/>
-      <c r="AG11" s="4" t="inlineStr"/>
-      <c r="AH11" s="4" t="inlineStr"/>
-      <c r="AI11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ11" s="4" t="inlineStr"/>
-      <c r="AK11" s="4" t="inlineStr"/>
-      <c r="AL11" s="4" t="inlineStr"/>
-      <c r="AM11" s="4" t="inlineStr"/>
-      <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr"/>
-      <c r="AP11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -2049,28 +1905,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC12" s="4" t="inlineStr"/>
-      <c r="AD12" s="4" t="inlineStr">
+      <c r="AC12" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
+      <c r="AD12" s="4" t="inlineStr"/>
       <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="inlineStr"/>
-      <c r="AG12" s="4" t="inlineStr"/>
-      <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr"/>
-      <c r="AL12" s="4" t="inlineStr"/>
-      <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr"/>
-      <c r="AP12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -2173,28 +2020,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC13" s="4" t="inlineStr"/>
-      <c r="AD13" s="4" t="inlineStr">
+      <c r="AC13" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
+      <c r="AD13" s="4" t="inlineStr"/>
       <c r="AE13" s="4" t="inlineStr"/>
-      <c r="AF13" s="4" t="inlineStr"/>
-      <c r="AG13" s="4" t="inlineStr"/>
-      <c r="AH13" s="4" t="inlineStr"/>
-      <c r="AI13" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ13" s="4" t="inlineStr"/>
-      <c r="AK13" s="4" t="inlineStr"/>
-      <c r="AL13" s="4" t="inlineStr"/>
-      <c r="AM13" s="4" t="inlineStr"/>
-      <c r="AN13" s="4" t="inlineStr"/>
-      <c r="AO13" s="4" t="inlineStr"/>
-      <c r="AP13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -2293,28 +2131,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC14" s="4" t="inlineStr"/>
-      <c r="AD14" s="4" t="inlineStr">
+      <c r="AC14" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
+      <c r="AD14" s="4" t="inlineStr"/>
       <c r="AE14" s="4" t="inlineStr"/>
-      <c r="AF14" s="4" t="inlineStr"/>
-      <c r="AG14" s="4" t="inlineStr"/>
-      <c r="AH14" s="4" t="inlineStr"/>
-      <c r="AI14" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ14" s="4" t="inlineStr"/>
-      <c r="AK14" s="4" t="inlineStr"/>
-      <c r="AL14" s="4" t="inlineStr"/>
-      <c r="AM14" s="4" t="inlineStr"/>
-      <c r="AN14" s="4" t="inlineStr"/>
-      <c r="AO14" s="4" t="inlineStr"/>
-      <c r="AP14" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -2417,28 +2246,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC15" s="4" t="inlineStr"/>
-      <c r="AD15" s="4" t="inlineStr">
+      <c r="AC15" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
+      <c r="AD15" s="4" t="inlineStr"/>
       <c r="AE15" s="4" t="inlineStr"/>
-      <c r="AF15" s="4" t="inlineStr"/>
-      <c r="AG15" s="4" t="inlineStr"/>
-      <c r="AH15" s="4" t="inlineStr"/>
-      <c r="AI15" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ15" s="4" t="inlineStr"/>
-      <c r="AK15" s="4" t="inlineStr"/>
-      <c r="AL15" s="4" t="inlineStr"/>
-      <c r="AM15" s="4" t="inlineStr"/>
-      <c r="AN15" s="4" t="inlineStr"/>
-      <c r="AO15" s="4" t="inlineStr"/>
-      <c r="AP15" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -2537,28 +2357,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC16" s="4" t="inlineStr"/>
-      <c r="AD16" s="4" t="inlineStr">
+      <c r="AC16" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
+      <c r="AD16" s="4" t="inlineStr"/>
       <c r="AE16" s="4" t="inlineStr"/>
-      <c r="AF16" s="4" t="inlineStr"/>
-      <c r="AG16" s="4" t="inlineStr"/>
-      <c r="AH16" s="4" t="inlineStr"/>
-      <c r="AI16" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ16" s="4" t="inlineStr"/>
-      <c r="AK16" s="4" t="inlineStr"/>
-      <c r="AL16" s="4" t="inlineStr"/>
-      <c r="AM16" s="4" t="inlineStr"/>
-      <c r="AN16" s="4" t="inlineStr"/>
-      <c r="AO16" s="4" t="inlineStr"/>
-      <c r="AP16" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -2658,27 +2469,18 @@
         </is>
       </c>
       <c r="AC17" s="4" t="inlineStr"/>
-      <c r="AD17" s="4" t="inlineStr"/>
+      <c r="AD17" s="4" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="AE17" s="4" t="inlineStr"/>
-      <c r="AF17" s="4" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="AG17" s="4" t="inlineStr"/>
-      <c r="AH17" s="4" t="inlineStr"/>
-      <c r="AI17" s="4" t="n">
+      <c r="AF17" s="4" t="n">
         <v>5.32</v>
       </c>
-      <c r="AJ17" s="4" t="inlineStr"/>
-      <c r="AK17" s="4" t="inlineStr"/>
-      <c r="AL17" s="4" t="inlineStr"/>
-      <c r="AM17" s="4" t="inlineStr"/>
-      <c r="AN17" s="4" t="inlineStr"/>
-      <c r="AO17" s="4" t="inlineStr"/>
-      <c r="AP17" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -2778,27 +2580,18 @@
         </is>
       </c>
       <c r="AC18" s="4" t="inlineStr"/>
-      <c r="AD18" s="4" t="inlineStr"/>
+      <c r="AD18" s="4" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
       <c r="AE18" s="4" t="inlineStr"/>
-      <c r="AF18" s="4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="AG18" s="4" t="inlineStr"/>
-      <c r="AH18" s="4" t="inlineStr"/>
-      <c r="AI18" s="4" t="n">
+      <c r="AF18" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="AJ18" s="4" t="inlineStr"/>
-      <c r="AK18" s="4" t="inlineStr"/>
-      <c r="AL18" s="4" t="inlineStr"/>
-      <c r="AM18" s="4" t="inlineStr"/>
-      <c r="AN18" s="4" t="inlineStr"/>
-      <c r="AO18" s="4" t="inlineStr"/>
-      <c r="AP18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -2898,27 +2691,18 @@
         </is>
       </c>
       <c r="AC19" s="4" t="inlineStr"/>
-      <c r="AD19" s="4" t="inlineStr"/>
+      <c r="AD19" s="4" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
       <c r="AE19" s="4" t="inlineStr"/>
-      <c r="AF19" s="4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="AG19" s="4" t="inlineStr"/>
-      <c r="AH19" s="4" t="inlineStr"/>
-      <c r="AI19" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ19" s="4" t="inlineStr"/>
-      <c r="AK19" s="4" t="inlineStr"/>
-      <c r="AL19" s="4" t="inlineStr"/>
-      <c r="AM19" s="4" t="inlineStr"/>
-      <c r="AN19" s="4" t="inlineStr"/>
-      <c r="AO19" s="4" t="inlineStr"/>
-      <c r="AP19" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF19" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -3018,27 +2802,18 @@
         </is>
       </c>
       <c r="AC20" s="4" t="inlineStr"/>
-      <c r="AD20" s="4" t="inlineStr"/>
+      <c r="AD20" s="4" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
       <c r="AE20" s="4" t="inlineStr"/>
-      <c r="AF20" s="4" t="inlineStr">
-        <is>
-          <t>Chemicals</t>
-        </is>
-      </c>
-      <c r="AG20" s="4" t="inlineStr"/>
-      <c r="AH20" s="4" t="inlineStr"/>
-      <c r="AI20" s="4" t="n">
+      <c r="AF20" s="4" t="n">
         <v>1.38</v>
       </c>
-      <c r="AJ20" s="4" t="inlineStr"/>
-      <c r="AK20" s="4" t="inlineStr"/>
-      <c r="AL20" s="4" t="inlineStr"/>
-      <c r="AM20" s="4" t="inlineStr"/>
-      <c r="AN20" s="4" t="inlineStr"/>
-      <c r="AO20" s="4" t="inlineStr"/>
-      <c r="AP20" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -3138,27 +2913,18 @@
         </is>
       </c>
       <c r="AC21" s="4" t="inlineStr"/>
-      <c r="AD21" s="4" t="inlineStr"/>
+      <c r="AD21" s="4" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
       <c r="AE21" s="4" t="inlineStr"/>
-      <c r="AF21" s="4" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="AG21" s="4" t="inlineStr"/>
-      <c r="AH21" s="4" t="inlineStr"/>
-      <c r="AI21" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ21" s="4" t="inlineStr"/>
-      <c r="AK21" s="4" t="inlineStr"/>
-      <c r="AL21" s="4" t="inlineStr"/>
-      <c r="AM21" s="4" t="inlineStr"/>
-      <c r="AN21" s="4" t="inlineStr"/>
-      <c r="AO21" s="4" t="inlineStr"/>
-      <c r="AP21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF21" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -3258,27 +3024,18 @@
         </is>
       </c>
       <c r="AC22" s="4" t="inlineStr"/>
-      <c r="AD22" s="4" t="inlineStr"/>
+      <c r="AD22" s="4" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="AE22" s="4" t="inlineStr"/>
-      <c r="AF22" s="4" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="AG22" s="4" t="inlineStr"/>
-      <c r="AH22" s="4" t="inlineStr"/>
-      <c r="AI22" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ22" s="4" t="inlineStr"/>
-      <c r="AK22" s="4" t="inlineStr"/>
-      <c r="AL22" s="4" t="inlineStr"/>
-      <c r="AM22" s="4" t="inlineStr"/>
-      <c r="AN22" s="4" t="inlineStr"/>
-      <c r="AO22" s="4" t="inlineStr"/>
-      <c r="AP22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF22" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -3378,27 +3135,18 @@
         </is>
       </c>
       <c r="AC23" s="4" t="inlineStr"/>
-      <c r="AD23" s="4" t="inlineStr"/>
+      <c r="AD23" s="4" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
       <c r="AE23" s="4" t="inlineStr"/>
-      <c r="AF23" s="4" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="AG23" s="4" t="inlineStr"/>
-      <c r="AH23" s="4" t="inlineStr"/>
-      <c r="AI23" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ23" s="4" t="inlineStr"/>
-      <c r="AK23" s="4" t="inlineStr"/>
-      <c r="AL23" s="4" t="inlineStr"/>
-      <c r="AM23" s="4" t="inlineStr"/>
-      <c r="AN23" s="4" t="inlineStr"/>
-      <c r="AO23" s="4" t="inlineStr"/>
-      <c r="AP23" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF23" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -3498,27 +3246,18 @@
         </is>
       </c>
       <c r="AC24" s="4" t="inlineStr"/>
-      <c r="AD24" s="4" t="inlineStr"/>
+      <c r="AD24" s="4" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
       <c r="AE24" s="4" t="inlineStr"/>
-      <c r="AF24" s="4" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="AG24" s="4" t="inlineStr"/>
-      <c r="AH24" s="4" t="inlineStr"/>
-      <c r="AI24" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ24" s="4" t="inlineStr"/>
-      <c r="AK24" s="4" t="inlineStr"/>
-      <c r="AL24" s="4" t="inlineStr"/>
-      <c r="AM24" s="4" t="inlineStr"/>
-      <c r="AN24" s="4" t="inlineStr"/>
-      <c r="AO24" s="4" t="inlineStr"/>
-      <c r="AP24" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -3618,27 +3357,18 @@
         </is>
       </c>
       <c r="AC25" s="4" t="inlineStr"/>
-      <c r="AD25" s="4" t="inlineStr"/>
+      <c r="AD25" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
       <c r="AE25" s="4" t="inlineStr"/>
-      <c r="AF25" s="4" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="AG25" s="4" t="inlineStr"/>
-      <c r="AH25" s="4" t="inlineStr"/>
-      <c r="AI25" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ25" s="4" t="inlineStr"/>
-      <c r="AK25" s="4" t="inlineStr"/>
-      <c r="AL25" s="4" t="inlineStr"/>
-      <c r="AM25" s="4" t="inlineStr"/>
-      <c r="AN25" s="4" t="inlineStr"/>
-      <c r="AO25" s="4" t="inlineStr"/>
-      <c r="AP25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF25" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -3738,27 +3468,18 @@
         </is>
       </c>
       <c r="AC26" s="4" t="inlineStr"/>
-      <c r="AD26" s="4" t="inlineStr"/>
+      <c r="AD26" s="4" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
       <c r="AE26" s="4" t="inlineStr"/>
-      <c r="AF26" s="4" t="inlineStr">
-        <is>
-          <t>Metal</t>
-        </is>
-      </c>
-      <c r="AG26" s="4" t="inlineStr"/>
-      <c r="AH26" s="4" t="inlineStr"/>
-      <c r="AI26" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ26" s="4" t="inlineStr"/>
-      <c r="AK26" s="4" t="inlineStr"/>
-      <c r="AL26" s="4" t="inlineStr"/>
-      <c r="AM26" s="4" t="inlineStr"/>
-      <c r="AN26" s="4" t="inlineStr"/>
-      <c r="AO26" s="4" t="inlineStr"/>
-      <c r="AP26" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF26" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -3854,27 +3575,18 @@
         </is>
       </c>
       <c r="AC27" s="4" t="inlineStr"/>
-      <c r="AD27" s="4" t="inlineStr"/>
+      <c r="AD27" s="4" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
       <c r="AE27" s="4" t="inlineStr"/>
-      <c r="AF27" s="4" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="AG27" s="4" t="inlineStr"/>
-      <c r="AH27" s="4" t="inlineStr"/>
-      <c r="AI27" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ27" s="4" t="inlineStr"/>
-      <c r="AK27" s="4" t="inlineStr"/>
-      <c r="AL27" s="4" t="inlineStr"/>
-      <c r="AM27" s="4" t="inlineStr"/>
-      <c r="AN27" s="4" t="inlineStr"/>
-      <c r="AO27" s="4" t="inlineStr"/>
-      <c r="AP27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF27" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -3981,30 +3693,21 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC28" s="4" t="inlineStr"/>
-      <c r="AD28" s="4" t="inlineStr">
+      <c r="AC28" s="4" t="inlineStr">
         <is>
           <t>Momentum · Value · Trend</t>
         </is>
       </c>
-      <c r="AE28" s="4" t="inlineStr"/>
-      <c r="AF28" s="4" t="inlineStr"/>
-      <c r="AG28" s="4" t="inlineStr"/>
-      <c r="AH28" s="4" t="n">
+      <c r="AD28" s="4" t="inlineStr"/>
+      <c r="AE28" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AI28" s="4" t="n">
+      <c r="AF28" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AJ28" s="4" t="inlineStr"/>
-      <c r="AK28" s="4" t="inlineStr"/>
-      <c r="AL28" s="4" t="inlineStr"/>
-      <c r="AM28" s="4" t="inlineStr"/>
-      <c r="AN28" s="4" t="inlineStr"/>
-      <c r="AO28" s="4" t="inlineStr"/>
-      <c r="AP28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -4111,28 +3814,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC29" s="4" t="inlineStr"/>
-      <c r="AD29" s="4" t="inlineStr">
+      <c r="AC29" s="4" t="inlineStr">
         <is>
           <t>Momentum · Trend · Quality</t>
         </is>
       </c>
+      <c r="AD29" s="4" t="inlineStr"/>
       <c r="AE29" s="4" t="inlineStr"/>
-      <c r="AF29" s="4" t="inlineStr"/>
-      <c r="AG29" s="4" t="inlineStr"/>
-      <c r="AH29" s="4" t="inlineStr"/>
-      <c r="AI29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="4" t="inlineStr"/>
-      <c r="AK29" s="4" t="inlineStr"/>
-      <c r="AL29" s="4" t="inlineStr"/>
-      <c r="AM29" s="4" t="inlineStr"/>
-      <c r="AN29" s="4" t="inlineStr"/>
-      <c r="AO29" s="4" t="inlineStr"/>
-      <c r="AP29" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -4239,28 +3933,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC30" s="4" t="inlineStr"/>
-      <c r="AD30" s="4" t="inlineStr">
+      <c r="AC30" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · Mean Reversion</t>
         </is>
       </c>
+      <c r="AD30" s="4" t="inlineStr"/>
       <c r="AE30" s="4" t="inlineStr"/>
-      <c r="AF30" s="4" t="inlineStr"/>
-      <c r="AG30" s="4" t="inlineStr"/>
-      <c r="AH30" s="4" t="inlineStr"/>
-      <c r="AI30" s="4" t="n">
+      <c r="AF30" s="4" t="n">
         <v>12.15</v>
       </c>
-      <c r="AJ30" s="4" t="inlineStr"/>
-      <c r="AK30" s="4" t="inlineStr"/>
-      <c r="AL30" s="4" t="inlineStr"/>
-      <c r="AM30" s="4" t="inlineStr"/>
-      <c r="AN30" s="4" t="inlineStr"/>
-      <c r="AO30" s="4" t="inlineStr"/>
-      <c r="AP30" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -4367,28 +4052,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC31" s="4" t="inlineStr"/>
-      <c r="AD31" s="4" t="inlineStr">
+      <c r="AC31" s="4" t="inlineStr">
         <is>
           <t>Momentum · Value · Mean Reversion</t>
         </is>
       </c>
+      <c r="AD31" s="4" t="inlineStr"/>
       <c r="AE31" s="4" t="inlineStr"/>
-      <c r="AF31" s="4" t="inlineStr"/>
-      <c r="AG31" s="4" t="inlineStr"/>
-      <c r="AH31" s="4" t="inlineStr"/>
-      <c r="AI31" s="4" t="n">
+      <c r="AF31" s="4" t="n">
         <v>12.97</v>
       </c>
-      <c r="AJ31" s="4" t="inlineStr"/>
-      <c r="AK31" s="4" t="inlineStr"/>
-      <c r="AL31" s="4" t="inlineStr"/>
-      <c r="AM31" s="4" t="inlineStr"/>
-      <c r="AN31" s="4" t="inlineStr"/>
-      <c r="AO31" s="4" t="inlineStr"/>
-      <c r="AP31" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG31" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -4495,28 +4171,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC32" s="4" t="inlineStr"/>
-      <c r="AD32" s="4" t="inlineStr">
+      <c r="AC32" s="4" t="inlineStr">
         <is>
           <t>Mean Reversion · Growth · Value</t>
         </is>
       </c>
+      <c r="AD32" s="4" t="inlineStr"/>
       <c r="AE32" s="4" t="inlineStr"/>
-      <c r="AF32" s="4" t="inlineStr"/>
-      <c r="AG32" s="4" t="inlineStr"/>
-      <c r="AH32" s="4" t="inlineStr"/>
-      <c r="AI32" s="4" t="n">
+      <c r="AF32" s="4" t="n">
         <v>14.45</v>
       </c>
-      <c r="AJ32" s="4" t="inlineStr"/>
-      <c r="AK32" s="4" t="inlineStr"/>
-      <c r="AL32" s="4" t="inlineStr"/>
-      <c r="AM32" s="4" t="inlineStr"/>
-      <c r="AN32" s="4" t="inlineStr"/>
-      <c r="AO32" s="4" t="inlineStr"/>
-      <c r="AP32" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG32" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -4623,28 +4290,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC33" s="4" t="inlineStr"/>
-      <c r="AD33" s="4" t="inlineStr">
+      <c r="AC33" s="4" t="inlineStr">
         <is>
           <t>Value · News · Event Driven</t>
         </is>
       </c>
+      <c r="AD33" s="4" t="inlineStr"/>
       <c r="AE33" s="4" t="inlineStr"/>
-      <c r="AF33" s="4" t="inlineStr"/>
-      <c r="AG33" s="4" t="inlineStr"/>
-      <c r="AH33" s="4" t="inlineStr"/>
-      <c r="AI33" s="4" t="n">
+      <c r="AF33" s="4" t="n">
         <v>14.77</v>
       </c>
-      <c r="AJ33" s="4" t="inlineStr"/>
-      <c r="AK33" s="4" t="inlineStr"/>
-      <c r="AL33" s="4" t="inlineStr"/>
-      <c r="AM33" s="4" t="inlineStr"/>
-      <c r="AN33" s="4" t="inlineStr"/>
-      <c r="AO33" s="4" t="inlineStr"/>
-      <c r="AP33" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG33" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -4751,28 +4409,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC34" s="4" t="inlineStr"/>
-      <c r="AD34" s="4" t="inlineStr">
+      <c r="AC34" s="4" t="inlineStr">
         <is>
           <t>Value · Trend · Momentum</t>
         </is>
       </c>
+      <c r="AD34" s="4" t="inlineStr"/>
       <c r="AE34" s="4" t="inlineStr"/>
-      <c r="AF34" s="4" t="inlineStr"/>
-      <c r="AG34" s="4" t="inlineStr"/>
-      <c r="AH34" s="4" t="inlineStr"/>
-      <c r="AI34" s="4" t="n">
+      <c r="AF34" s="4" t="n">
         <v>14.87</v>
       </c>
-      <c r="AJ34" s="4" t="inlineStr"/>
-      <c r="AK34" s="4" t="inlineStr"/>
-      <c r="AL34" s="4" t="inlineStr"/>
-      <c r="AM34" s="4" t="inlineStr"/>
-      <c r="AN34" s="4" t="inlineStr"/>
-      <c r="AO34" s="4" t="inlineStr"/>
-      <c r="AP34" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG34" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -4879,28 +4528,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC35" s="4" t="inlineStr"/>
-      <c r="AD35" s="4" t="inlineStr">
+      <c r="AC35" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Trend</t>
         </is>
       </c>
+      <c r="AD35" s="4" t="inlineStr"/>
       <c r="AE35" s="4" t="inlineStr"/>
-      <c r="AF35" s="4" t="inlineStr"/>
-      <c r="AG35" s="4" t="inlineStr"/>
-      <c r="AH35" s="4" t="inlineStr"/>
-      <c r="AI35" s="4" t="n">
+      <c r="AF35" s="4" t="n">
         <v>15.21</v>
       </c>
-      <c r="AJ35" s="4" t="inlineStr"/>
-      <c r="AK35" s="4" t="inlineStr"/>
-      <c r="AL35" s="4" t="inlineStr"/>
-      <c r="AM35" s="4" t="inlineStr"/>
-      <c r="AN35" s="4" t="inlineStr"/>
-      <c r="AO35" s="4" t="inlineStr"/>
-      <c r="AP35" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG35" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -5007,28 +4647,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC36" s="4" t="inlineStr"/>
-      <c r="AD36" s="4" t="inlineStr">
+      <c r="AC36" s="4" t="inlineStr">
         <is>
           <t>Momentum · News · Quality</t>
         </is>
       </c>
+      <c r="AD36" s="4" t="inlineStr"/>
       <c r="AE36" s="4" t="inlineStr"/>
-      <c r="AF36" s="4" t="inlineStr"/>
-      <c r="AG36" s="4" t="inlineStr"/>
-      <c r="AH36" s="4" t="inlineStr"/>
-      <c r="AI36" s="4" t="n">
+      <c r="AF36" s="4" t="n">
         <v>15.5</v>
       </c>
-      <c r="AJ36" s="4" t="inlineStr"/>
-      <c r="AK36" s="4" t="inlineStr"/>
-      <c r="AL36" s="4" t="inlineStr"/>
-      <c r="AM36" s="4" t="inlineStr"/>
-      <c r="AN36" s="4" t="inlineStr"/>
-      <c r="AO36" s="4" t="inlineStr"/>
-      <c r="AP36" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG36" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -5135,28 +4766,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC37" s="4" t="inlineStr"/>
-      <c r="AD37" s="4" t="inlineStr">
+      <c r="AC37" s="4" t="inlineStr">
         <is>
           <t>Momentum · News · Value</t>
         </is>
       </c>
+      <c r="AD37" s="4" t="inlineStr"/>
       <c r="AE37" s="4" t="inlineStr"/>
-      <c r="AF37" s="4" t="inlineStr"/>
-      <c r="AG37" s="4" t="inlineStr"/>
-      <c r="AH37" s="4" t="inlineStr"/>
-      <c r="AI37" s="4" t="n">
+      <c r="AF37" s="4" t="n">
         <v>16.4</v>
       </c>
-      <c r="AJ37" s="4" t="inlineStr"/>
-      <c r="AK37" s="4" t="inlineStr"/>
-      <c r="AL37" s="4" t="inlineStr"/>
-      <c r="AM37" s="4" t="inlineStr"/>
-      <c r="AN37" s="4" t="inlineStr"/>
-      <c r="AO37" s="4" t="inlineStr"/>
-      <c r="AP37" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG37" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -5263,28 +4885,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC38" s="4" t="inlineStr"/>
-      <c r="AD38" s="4" t="inlineStr">
+      <c r="AC38" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
+      <c r="AD38" s="4" t="inlineStr"/>
       <c r="AE38" s="4" t="inlineStr"/>
-      <c r="AF38" s="4" t="inlineStr"/>
-      <c r="AG38" s="4" t="inlineStr"/>
-      <c r="AH38" s="4" t="inlineStr"/>
-      <c r="AI38" s="4" t="n">
+      <c r="AF38" s="4" t="n">
         <v>37.17</v>
       </c>
-      <c r="AJ38" s="4" t="inlineStr"/>
-      <c r="AK38" s="4" t="inlineStr"/>
-      <c r="AL38" s="4" t="inlineStr"/>
-      <c r="AM38" s="4" t="inlineStr"/>
-      <c r="AN38" s="4" t="inlineStr"/>
-      <c r="AO38" s="4" t="inlineStr"/>
-      <c r="AP38" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG38" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -5391,28 +5004,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC39" s="4" t="inlineStr"/>
-      <c r="AD39" s="4" t="inlineStr">
+      <c r="AC39" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
+      <c r="AD39" s="4" t="inlineStr"/>
       <c r="AE39" s="4" t="inlineStr"/>
-      <c r="AF39" s="4" t="inlineStr"/>
-      <c r="AG39" s="4" t="inlineStr"/>
-      <c r="AH39" s="4" t="inlineStr"/>
-      <c r="AI39" s="4" t="n">
+      <c r="AF39" s="4" t="n">
         <v>37.79</v>
       </c>
-      <c r="AJ39" s="4" t="inlineStr"/>
-      <c r="AK39" s="4" t="inlineStr"/>
-      <c r="AL39" s="4" t="inlineStr"/>
-      <c r="AM39" s="4" t="inlineStr"/>
-      <c r="AN39" s="4" t="inlineStr"/>
-      <c r="AO39" s="4" t="inlineStr"/>
-      <c r="AP39" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG39" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -5519,28 +5123,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC40" s="4" t="inlineStr"/>
-      <c r="AD40" s="4" t="inlineStr">
+      <c r="AC40" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
+      <c r="AD40" s="4" t="inlineStr"/>
       <c r="AE40" s="4" t="inlineStr"/>
-      <c r="AF40" s="4" t="inlineStr"/>
-      <c r="AG40" s="4" t="inlineStr"/>
-      <c r="AH40" s="4" t="inlineStr"/>
-      <c r="AI40" s="4" t="n">
+      <c r="AF40" s="4" t="n">
         <v>43.85</v>
       </c>
-      <c r="AJ40" s="4" t="inlineStr"/>
-      <c r="AK40" s="4" t="inlineStr"/>
-      <c r="AL40" s="4" t="inlineStr"/>
-      <c r="AM40" s="4" t="inlineStr"/>
-      <c r="AN40" s="4" t="inlineStr"/>
-      <c r="AO40" s="4" t="inlineStr"/>
-      <c r="AP40" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG40" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -5647,28 +5242,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC41" s="4" t="inlineStr"/>
-      <c r="AD41" s="4" t="inlineStr">
+      <c r="AC41" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
+      <c r="AD41" s="4" t="inlineStr"/>
       <c r="AE41" s="4" t="inlineStr"/>
-      <c r="AF41" s="4" t="inlineStr"/>
-      <c r="AG41" s="4" t="inlineStr"/>
-      <c r="AH41" s="4" t="inlineStr"/>
-      <c r="AI41" s="4" t="n">
+      <c r="AF41" s="4" t="n">
         <v>45.62</v>
       </c>
-      <c r="AJ41" s="4" t="inlineStr"/>
-      <c r="AK41" s="4" t="inlineStr"/>
-      <c r="AL41" s="4" t="inlineStr"/>
-      <c r="AM41" s="4" t="inlineStr"/>
-      <c r="AN41" s="4" t="inlineStr"/>
-      <c r="AO41" s="4" t="inlineStr"/>
-      <c r="AP41" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG41" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -5775,33 +5361,24 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC42" s="4" t="inlineStr"/>
-      <c r="AD42" s="4" t="inlineStr">
+      <c r="AC42" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
+      <c r="AD42" s="4" t="inlineStr"/>
       <c r="AE42" s="4" t="inlineStr"/>
-      <c r="AF42" s="4" t="inlineStr"/>
-      <c r="AG42" s="4" t="inlineStr"/>
-      <c r="AH42" s="4" t="inlineStr"/>
-      <c r="AI42" s="4" t="n">
+      <c r="AF42" s="4" t="n">
         <v>45.94</v>
       </c>
-      <c r="AJ42" s="4" t="inlineStr"/>
-      <c r="AK42" s="4" t="inlineStr"/>
-      <c r="AL42" s="4" t="inlineStr"/>
-      <c r="AM42" s="4" t="inlineStr"/>
-      <c r="AN42" s="4" t="inlineStr"/>
-      <c r="AO42" s="4" t="inlineStr"/>
-      <c r="AP42" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG42" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP42"/>
+  <autoFilter ref="A1:AG42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_daily_2026-08-01.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-01.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AG$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AJ$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -66,8 +66,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD966"/>
-        <bgColor rgb="00FFD966"/>
+        <fgColor rgb="00F8CBAD"/>
+        <bgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG42"/>
+  <dimension ref="A1:AJ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -480,33 +480,36 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
     <col width="11" customWidth="1" min="23" max="23"/>
     <col width="8" customWidth="1" min="24" max="24"/>
-    <col width="15" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="32" customWidth="1" min="29" max="29"/>
-    <col width="20" customWidth="1" min="30" max="30"/>
-    <col width="18" customWidth="1" min="31" max="31"/>
-    <col width="17" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="31" max="31"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
     <col width="20" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="34" max="34"/>
+    <col width="17" customWidth="1" min="35" max="35"/>
+    <col width="20" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -542,135 +545,150 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Exit Reason</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Exit P&amp;L %</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Confidence %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Conf Type</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Model Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Horizon (d)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Days Left</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Entry Price</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Buy Zone Low</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Buy Zone High</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Stop Loss</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Risk %</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Target 1</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>T1 %</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Target 2</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>T2 %</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Today Move %</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Current Perf %</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Max Gain %</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Max DD %</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Lifecycle State</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Top Drivers</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Portfolio Weight %</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Expected Alpha %</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Last Updated (UTC)</t>
         </is>
@@ -707,87 +725,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="J2" s="4" t="n">
         <v>39.3</v>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="L2" s="4" t="n">
         <v>26.3</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="M2" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="N2" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M2" s="4" t="n">
+      <c r="O2" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="n">
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q2" s="4" t="n">
         <v>2452.2</v>
       </c>
-      <c r="P2" s="4" t="n">
+      <c r="R2" s="4" t="n">
         <v>2452.2</v>
       </c>
-      <c r="Q2" s="4" t="n">
+      <c r="S2" s="4" t="n">
         <v>2427.68</v>
       </c>
-      <c r="R2" s="4" t="n">
+      <c r="T2" s="4" t="n">
         <v>2476.72</v>
       </c>
-      <c r="S2" s="4" t="n">
+      <c r="U2" s="4" t="n">
         <v>2329.59</v>
       </c>
-      <c r="T2" s="4" t="n">
+      <c r="V2" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U2" s="4" t="n">
+      <c r="W2" s="4" t="n">
         <v>2648.38</v>
       </c>
-      <c r="V2" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W2" s="4" t="n">
+      <c r="X2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y2" s="4" t="n">
         <v>2820.03</v>
       </c>
-      <c r="X2" s="4" t="n">
+      <c r="Z2" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="4" t="inlineStr"/>
-      <c r="AA2" s="4" t="inlineStr"/>
-      <c r="AB2" s="4" t="inlineStr">
+      <c r="AA2" s="4" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="AB2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AD2" s="4" t="inlineStr"/>
+      <c r="AE2" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC2" s="4" t="inlineStr">
+      <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Ai Hybrid</t>
         </is>
       </c>
-      <c r="AD2" s="4" t="inlineStr"/>
-      <c r="AE2" s="4" t="inlineStr"/>
-      <c r="AF2" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG2" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG2" s="4" t="inlineStr"/>
+      <c r="AH2" s="4" t="inlineStr"/>
+      <c r="AI2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -822,87 +845,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="J3" s="4" t="n">
         <v>40.6</v>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>26.2</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="M3" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="N3" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="n">
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="n">
         <v>5196.6</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>5196.6</v>
       </c>
-      <c r="Q3" s="4" t="n">
+      <c r="S3" s="4" t="n">
         <v>5144.63</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="T3" s="4" t="n">
         <v>5248.57</v>
       </c>
-      <c r="S3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>4936.77</v>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="V3" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="W3" s="4" t="n">
         <v>5612.33</v>
       </c>
-      <c r="V3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W3" s="4" t="n">
+      <c r="X3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y3" s="4" t="n">
         <v>5976.09</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="Z3" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="4" t="inlineStr"/>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AB3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AD3" s="4" t="inlineStr"/>
+      <c r="AE3" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC3" s="4" t="inlineStr">
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · Ai Hybrid</t>
         </is>
       </c>
-      <c r="AD3" s="4" t="inlineStr"/>
-      <c r="AE3" s="4" t="inlineStr"/>
-      <c r="AF3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG3" s="4" t="inlineStr"/>
+      <c r="AH3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -933,87 +961,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="J4" s="4" t="n">
         <v>39.3</v>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="L4" s="4" t="n">
         <v>24.3</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="M4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="N4" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="O4" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="n">
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="n">
         <v>133.14</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="R4" s="4" t="n">
         <v>133.14</v>
       </c>
-      <c r="Q4" s="4" t="n">
+      <c r="S4" s="4" t="n">
         <v>131.81</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="T4" s="4" t="n">
         <v>134.47</v>
       </c>
-      <c r="S4" s="4" t="n">
+      <c r="U4" s="4" t="n">
         <v>126.48</v>
       </c>
-      <c r="T4" s="4" t="n">
+      <c r="V4" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="W4" s="4" t="n">
         <v>143.79</v>
       </c>
-      <c r="V4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W4" s="4" t="n">
+      <c r="X4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y4" s="4" t="n">
         <v>153.11</v>
       </c>
-      <c r="X4" s="4" t="n">
+      <c r="Z4" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="4" t="inlineStr"/>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AB4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="4" t="inlineStr"/>
+      <c r="AD4" s="4" t="inlineStr"/>
+      <c r="AE4" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>Quality · Momentum · Ai Hybrid</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr"/>
-      <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG4" s="4" t="inlineStr"/>
+      <c r="AH4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -1044,87 +1077,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="J5" s="4" t="n">
         <v>40.7</v>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="L5" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="M5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="N5" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="O5" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="n">
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="n">
         <v>5524</v>
       </c>
-      <c r="P5" s="4" t="n">
+      <c r="R5" s="4" t="n">
         <v>5524</v>
       </c>
-      <c r="Q5" s="4" t="n">
+      <c r="S5" s="4" t="n">
         <v>5468.76</v>
       </c>
-      <c r="R5" s="4" t="n">
+      <c r="T5" s="4" t="n">
         <v>5579.24</v>
       </c>
-      <c r="S5" s="4" t="n">
+      <c r="U5" s="4" t="n">
         <v>5247.8</v>
       </c>
-      <c r="T5" s="4" t="n">
+      <c r="V5" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U5" s="4" t="n">
+      <c r="W5" s="4" t="n">
         <v>5965.92</v>
       </c>
-      <c r="V5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W5" s="4" t="n">
+      <c r="X5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y5" s="4" t="n">
         <v>6352.6</v>
       </c>
-      <c r="X5" s="4" t="n">
+      <c r="Z5" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="4" t="inlineStr"/>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="AB5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="4" t="inlineStr"/>
+      <c r="AD5" s="4" t="inlineStr"/>
+      <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC5" s="4" t="inlineStr">
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>Trend · Growth · Value</t>
         </is>
       </c>
-      <c r="AD5" s="4" t="inlineStr"/>
-      <c r="AE5" s="4" t="inlineStr"/>
-      <c r="AF5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG5" s="4" t="inlineStr"/>
+      <c r="AH5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -1159,87 +1197,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="J6" s="4" t="n">
         <v>43.1</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="L6" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="M6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="N6" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="O6" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="n">
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="n">
         <v>1346.6</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="R6" s="4" t="n">
         <v>1346.6</v>
       </c>
-      <c r="Q6" s="4" t="n">
+      <c r="S6" s="4" t="n">
         <v>1333.13</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="T6" s="4" t="n">
         <v>1360.07</v>
       </c>
-      <c r="S6" s="4" t="n">
+      <c r="U6" s="4" t="n">
         <v>1279.27</v>
       </c>
-      <c r="T6" s="4" t="n">
+      <c r="V6" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U6" s="4" t="n">
+      <c r="W6" s="4" t="n">
         <v>1454.33</v>
       </c>
-      <c r="V6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W6" s="4" t="n">
+      <c r="X6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y6" s="4" t="n">
         <v>1548.59</v>
       </c>
-      <c r="X6" s="4" t="n">
+      <c r="Z6" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="4" t="inlineStr"/>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="inlineStr">
+      <c r="AA6" s="4" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="AB6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AD6" s="4" t="inlineStr"/>
+      <c r="AE6" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC6" s="4" t="inlineStr">
+      <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Momentum</t>
         </is>
       </c>
-      <c r="AD6" s="4" t="inlineStr"/>
-      <c r="AE6" s="4" t="inlineStr"/>
-      <c r="AF6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -1270,87 +1313,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="J7" s="4" t="n">
         <v>46.4</v>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="L7" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="M7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="N7" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="O7" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="n">
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="n">
         <v>11602</v>
       </c>
-      <c r="P7" s="4" t="n">
+      <c r="R7" s="4" t="n">
         <v>11602</v>
       </c>
-      <c r="Q7" s="4" t="n">
+      <c r="S7" s="4" t="n">
         <v>11485.98</v>
       </c>
-      <c r="R7" s="4" t="n">
+      <c r="T7" s="4" t="n">
         <v>11718.02</v>
       </c>
-      <c r="S7" s="4" t="n">
+      <c r="U7" s="4" t="n">
         <v>11021.9</v>
       </c>
-      <c r="T7" s="4" t="n">
+      <c r="V7" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U7" s="4" t="n">
+      <c r="W7" s="4" t="n">
         <v>12530.16</v>
       </c>
-      <c r="V7" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W7" s="4" t="n">
+      <c r="X7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y7" s="4" t="n">
         <v>13342.3</v>
       </c>
-      <c r="X7" s="4" t="n">
+      <c r="Z7" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="4" t="inlineStr"/>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="inlineStr">
+      <c r="AA7" s="4" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="AB7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="4" t="inlineStr"/>
+      <c r="AD7" s="4" t="inlineStr"/>
+      <c r="AE7" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC7" s="4" t="inlineStr">
+      <c r="AF7" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · Momentum</t>
         </is>
       </c>
-      <c r="AD7" s="4" t="inlineStr"/>
-      <c r="AE7" s="4" t="inlineStr"/>
-      <c r="AF7" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG7" s="4" t="inlineStr"/>
+      <c r="AH7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -1381,87 +1429,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="J8" s="4" t="n">
         <v>40.7</v>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="L8" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="M8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="N8" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="O8" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="n">
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="n">
         <v>1158</v>
       </c>
-      <c r="P8" s="4" t="n">
+      <c r="R8" s="4" t="n">
         <v>1158</v>
       </c>
-      <c r="Q8" s="4" t="n">
+      <c r="S8" s="4" t="n">
         <v>1146.42</v>
       </c>
-      <c r="R8" s="4" t="n">
+      <c r="T8" s="4" t="n">
         <v>1169.58</v>
       </c>
-      <c r="S8" s="4" t="n">
+      <c r="U8" s="4" t="n">
         <v>1100.1</v>
       </c>
-      <c r="T8" s="4" t="n">
+      <c r="V8" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U8" s="4" t="n">
+      <c r="W8" s="4" t="n">
         <v>1250.64</v>
       </c>
-      <c r="V8" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W8" s="4" t="n">
+      <c r="X8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y8" s="4" t="n">
         <v>1331.7</v>
       </c>
-      <c r="X8" s="4" t="n">
+      <c r="Z8" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="4" t="inlineStr"/>
-      <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="inlineStr">
+      <c r="AA8" s="4" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="AB8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AD8" s="4" t="inlineStr"/>
+      <c r="AE8" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC8" s="4" t="inlineStr">
+      <c r="AF8" s="4" t="inlineStr">
         <is>
           <t>Mean Reversion · Quality · Momentum</t>
         </is>
       </c>
-      <c r="AD8" s="4" t="inlineStr"/>
-      <c r="AE8" s="4" t="inlineStr"/>
-      <c r="AF8" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG8" s="4" t="inlineStr"/>
+      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -1496,87 +1549,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H9" s="4" t="n">
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" s="4" t="n">
         <v>38.3</v>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="L9" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="M9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="N9" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="M9" s="4" t="n">
+      <c r="O9" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="n">
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n">
         <v>449.35</v>
       </c>
-      <c r="P9" s="4" t="n">
+      <c r="R9" s="4" t="n">
         <v>449.35</v>
       </c>
-      <c r="Q9" s="4" t="n">
+      <c r="S9" s="4" t="n">
         <v>444.86</v>
       </c>
-      <c r="R9" s="4" t="n">
+      <c r="T9" s="4" t="n">
         <v>453.84</v>
       </c>
-      <c r="S9" s="4" t="n">
+      <c r="U9" s="4" t="n">
         <v>426.88</v>
       </c>
-      <c r="T9" s="4" t="n">
+      <c r="V9" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U9" s="4" t="n">
+      <c r="W9" s="4" t="n">
         <v>485.3</v>
       </c>
-      <c r="V9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W9" s="4" t="n">
+      <c r="X9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y9" s="4" t="n">
         <v>516.75</v>
       </c>
-      <c r="X9" s="4" t="n">
+      <c r="Z9" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="4" t="inlineStr"/>
-      <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr">
+      <c r="AA9" s="4" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="AB9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="AD9" s="4" t="inlineStr"/>
+      <c r="AE9" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC9" s="4" t="inlineStr">
+      <c r="AF9" s="4" t="inlineStr">
         <is>
           <t>Value · Mean Reversion · Growth</t>
         </is>
       </c>
-      <c r="AD9" s="4" t="inlineStr"/>
-      <c r="AE9" s="4" t="inlineStr"/>
-      <c r="AF9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG9" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG9" s="4" t="inlineStr"/>
+      <c r="AH9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -1611,87 +1669,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="J10" s="4" t="n">
         <v>38.3</v>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="L10" s="4" t="n">
         <v>21.6</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="M10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="N10" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M10" s="4" t="n">
+      <c r="O10" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="n">
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="n">
         <v>287.2</v>
       </c>
-      <c r="P10" s="4" t="n">
+      <c r="R10" s="4" t="n">
         <v>287.2</v>
       </c>
-      <c r="Q10" s="4" t="n">
+      <c r="S10" s="4" t="n">
         <v>284.33</v>
       </c>
-      <c r="R10" s="4" t="n">
+      <c r="T10" s="4" t="n">
         <v>290.07</v>
       </c>
-      <c r="S10" s="4" t="n">
+      <c r="U10" s="4" t="n">
         <v>272.84</v>
       </c>
-      <c r="T10" s="4" t="n">
+      <c r="V10" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U10" s="4" t="n">
+      <c r="W10" s="4" t="n">
         <v>310.18</v>
       </c>
-      <c r="V10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W10" s="4" t="n">
+      <c r="X10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y10" s="4" t="n">
         <v>330.28</v>
       </c>
-      <c r="X10" s="4" t="n">
+      <c r="Z10" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="4" t="inlineStr"/>
-      <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="inlineStr">
+      <c r="AA10" s="4" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="AB10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="4" t="inlineStr"/>
+      <c r="AD10" s="4" t="inlineStr"/>
+      <c r="AE10" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC10" s="4" t="inlineStr">
+      <c r="AF10" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Value</t>
         </is>
       </c>
-      <c r="AD10" s="4" t="inlineStr"/>
-      <c r="AE10" s="4" t="inlineStr"/>
-      <c r="AF10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG10" s="4" t="inlineStr"/>
+      <c r="AH10" s="4" t="inlineStr"/>
+      <c r="AI10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -1722,87 +1785,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="J11" s="4" t="n">
         <v>38.3</v>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="L11" s="4" t="n">
         <v>20.7</v>
       </c>
-      <c r="K11" s="4" t="n">
+      <c r="M11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="N11" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="M11" s="4" t="n">
+      <c r="O11" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="n">
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="n">
         <v>10880</v>
       </c>
-      <c r="P11" s="4" t="n">
+      <c r="R11" s="4" t="n">
         <v>10880</v>
       </c>
-      <c r="Q11" s="4" t="n">
+      <c r="S11" s="4" t="n">
         <v>10771.2</v>
       </c>
-      <c r="R11" s="4" t="n">
+      <c r="T11" s="4" t="n">
         <v>10988.8</v>
       </c>
-      <c r="S11" s="4" t="n">
+      <c r="U11" s="4" t="n">
         <v>10336</v>
       </c>
-      <c r="T11" s="4" t="n">
+      <c r="V11" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U11" s="4" t="n">
+      <c r="W11" s="4" t="n">
         <v>11750.4</v>
       </c>
-      <c r="V11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W11" s="4" t="n">
+      <c r="X11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y11" s="4" t="n">
         <v>12512</v>
       </c>
-      <c r="X11" s="4" t="n">
+      <c r="Z11" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="4" t="inlineStr"/>
-      <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="inlineStr">
+      <c r="AA11" s="4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="4" t="inlineStr"/>
+      <c r="AD11" s="4" t="inlineStr"/>
+      <c r="AE11" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC11" s="4" t="inlineStr">
+      <c r="AF11" s="4" t="inlineStr">
         <is>
           <t>Value · Quality · Trend</t>
         </is>
       </c>
-      <c r="AD11" s="4" t="inlineStr"/>
-      <c r="AE11" s="4" t="inlineStr"/>
-      <c r="AF11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG11" s="4" t="inlineStr"/>
+      <c r="AH11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -1837,87 +1905,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="J12" s="4" t="n">
         <v>24.8</v>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="L12" s="4" t="n">
         <v>-26.6</v>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="M12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="N12" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M12" s="4" t="n">
+      <c r="O12" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="n">
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="n">
         <v>952.55</v>
       </c>
-      <c r="P12" s="4" t="n">
+      <c r="R12" s="4" t="n">
         <v>952.55</v>
       </c>
-      <c r="Q12" s="4" t="n">
+      <c r="S12" s="4" t="n">
         <v>943.02</v>
       </c>
-      <c r="R12" s="4" t="n">
+      <c r="T12" s="4" t="n">
         <v>962.08</v>
       </c>
-      <c r="S12" s="4" t="n">
+      <c r="U12" s="4" t="n">
         <v>904.92</v>
       </c>
-      <c r="T12" s="4" t="n">
+      <c r="V12" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U12" s="4" t="n">
+      <c r="W12" s="4" t="n">
         <v>1028.75</v>
       </c>
-      <c r="V12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W12" s="4" t="n">
+      <c r="X12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y12" s="4" t="n">
         <v>1095.43</v>
       </c>
-      <c r="X12" s="4" t="n">
+      <c r="Z12" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="4" t="inlineStr"/>
-      <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr">
+      <c r="AA12" s="4" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="AB12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="4" t="inlineStr"/>
+      <c r="AD12" s="4" t="inlineStr"/>
+      <c r="AE12" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC12" s="4" t="inlineStr">
+      <c r="AF12" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AD12" s="4" t="inlineStr"/>
-      <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG12" s="4" t="inlineStr"/>
+      <c r="AH12" s="4" t="inlineStr"/>
+      <c r="AI12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -1952,87 +2025,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="J13" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="L13" s="4" t="n">
         <v>-28.1</v>
       </c>
-      <c r="K13" s="4" t="n">
+      <c r="M13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="N13" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="M13" s="4" t="n">
+      <c r="O13" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O13" s="4" t="n">
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="n">
         <v>431.4</v>
       </c>
-      <c r="P13" s="4" t="n">
+      <c r="R13" s="4" t="n">
         <v>431.4</v>
       </c>
-      <c r="Q13" s="4" t="n">
+      <c r="S13" s="4" t="n">
         <v>427.09</v>
       </c>
-      <c r="R13" s="4" t="n">
+      <c r="T13" s="4" t="n">
         <v>435.71</v>
       </c>
-      <c r="S13" s="4" t="n">
+      <c r="U13" s="4" t="n">
         <v>409.83</v>
       </c>
-      <c r="T13" s="4" t="n">
+      <c r="V13" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U13" s="4" t="n">
+      <c r="W13" s="4" t="n">
         <v>465.91</v>
       </c>
-      <c r="V13" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W13" s="4" t="n">
+      <c r="X13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y13" s="4" t="n">
         <v>496.11</v>
       </c>
-      <c r="X13" s="4" t="n">
+      <c r="Z13" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="4" t="inlineStr"/>
-      <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr">
+      <c r="AA13" s="4" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="AB13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="4" t="inlineStr"/>
+      <c r="AD13" s="4" t="inlineStr"/>
+      <c r="AE13" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC13" s="4" t="inlineStr">
+      <c r="AF13" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AD13" s="4" t="inlineStr"/>
-      <c r="AE13" s="4" t="inlineStr"/>
-      <c r="AF13" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG13" s="4" t="inlineStr"/>
+      <c r="AH13" s="4" t="inlineStr"/>
+      <c r="AI13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -2063,87 +2141,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="J14" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="L14" s="4" t="n">
         <v>-28.4</v>
       </c>
-      <c r="K14" s="4" t="n">
+      <c r="M14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="N14" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M14" s="4" t="n">
+      <c r="O14" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="n">
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="n">
         <v>2157.8</v>
       </c>
-      <c r="P14" s="4" t="n">
+      <c r="R14" s="4" t="n">
         <v>2157.8</v>
       </c>
-      <c r="Q14" s="4" t="n">
+      <c r="S14" s="4" t="n">
         <v>2136.22</v>
       </c>
-      <c r="R14" s="4" t="n">
+      <c r="T14" s="4" t="n">
         <v>2179.38</v>
       </c>
-      <c r="S14" s="4" t="n">
+      <c r="U14" s="4" t="n">
         <v>2049.91</v>
       </c>
-      <c r="T14" s="4" t="n">
+      <c r="V14" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U14" s="4" t="n">
+      <c r="W14" s="4" t="n">
         <v>2330.42</v>
       </c>
-      <c r="V14" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W14" s="4" t="n">
+      <c r="X14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="4" t="n">
         <v>2481.47</v>
       </c>
-      <c r="X14" s="4" t="n">
+      <c r="Z14" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="4" t="inlineStr"/>
-      <c r="AA14" s="4" t="inlineStr"/>
-      <c r="AB14" s="4" t="inlineStr">
+      <c r="AA14" s="4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AB14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="4" t="inlineStr"/>
+      <c r="AD14" s="4" t="inlineStr"/>
+      <c r="AE14" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC14" s="4" t="inlineStr">
+      <c r="AF14" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AD14" s="4" t="inlineStr"/>
-      <c r="AE14" s="4" t="inlineStr"/>
-      <c r="AF14" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG14" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG14" s="4" t="inlineStr"/>
+      <c r="AH14" s="4" t="inlineStr"/>
+      <c r="AI14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -2178,87 +2261,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="J15" s="4" t="n">
         <v>24.8</v>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="L15" s="4" t="n">
         <v>-29.9</v>
       </c>
-      <c r="K15" s="4" t="n">
+      <c r="M15" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="N15" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M15" s="4" t="n">
+      <c r="O15" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="n">
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="n">
         <v>547.4</v>
       </c>
-      <c r="P15" s="4" t="n">
+      <c r="R15" s="4" t="n">
         <v>547.4</v>
       </c>
-      <c r="Q15" s="4" t="n">
+      <c r="S15" s="4" t="n">
         <v>541.9299999999999</v>
       </c>
-      <c r="R15" s="4" t="n">
+      <c r="T15" s="4" t="n">
         <v>552.87</v>
       </c>
-      <c r="S15" s="4" t="n">
+      <c r="U15" s="4" t="n">
         <v>520.03</v>
       </c>
-      <c r="T15" s="4" t="n">
+      <c r="V15" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U15" s="4" t="n">
+      <c r="W15" s="4" t="n">
         <v>591.1900000000001</v>
       </c>
-      <c r="V15" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W15" s="4" t="n">
+      <c r="X15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y15" s="4" t="n">
         <v>629.51</v>
       </c>
-      <c r="X15" s="4" t="n">
+      <c r="Z15" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="4" t="inlineStr"/>
-      <c r="AA15" s="4" t="inlineStr"/>
-      <c r="AB15" s="4" t="inlineStr">
+      <c r="AA15" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AD15" s="4" t="inlineStr"/>
+      <c r="AE15" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC15" s="4" t="inlineStr">
+      <c r="AF15" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AD15" s="4" t="inlineStr"/>
-      <c r="AE15" s="4" t="inlineStr"/>
-      <c r="AF15" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG15" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG15" s="4" t="inlineStr"/>
+      <c r="AH15" s="4" t="inlineStr"/>
+      <c r="AI15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -2289,87 +2377,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="J16" s="4" t="n">
         <v>28.4</v>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="L16" s="4" t="n">
         <v>-31.5</v>
       </c>
-      <c r="K16" s="4" t="n">
+      <c r="M16" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="N16" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M16" s="4" t="n">
+      <c r="O16" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="n">
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="n">
         <v>1363</v>
       </c>
-      <c r="P16" s="4" t="n">
+      <c r="R16" s="4" t="n">
         <v>1363</v>
       </c>
-      <c r="Q16" s="4" t="n">
+      <c r="S16" s="4" t="n">
         <v>1349.37</v>
       </c>
-      <c r="R16" s="4" t="n">
+      <c r="T16" s="4" t="n">
         <v>1376.63</v>
       </c>
-      <c r="S16" s="4" t="n">
+      <c r="U16" s="4" t="n">
         <v>1294.85</v>
       </c>
-      <c r="T16" s="4" t="n">
+      <c r="V16" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U16" s="4" t="n">
+      <c r="W16" s="4" t="n">
         <v>1472.04</v>
       </c>
-      <c r="V16" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W16" s="4" t="n">
+      <c r="X16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y16" s="4" t="n">
         <v>1567.45</v>
       </c>
-      <c r="X16" s="4" t="n">
+      <c r="Z16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="4" t="inlineStr"/>
-      <c r="AA16" s="4" t="inlineStr"/>
-      <c r="AB16" s="4" t="inlineStr">
+      <c r="AA16" s="4" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="AB16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="4" t="inlineStr"/>
+      <c r="AD16" s="4" t="inlineStr"/>
+      <c r="AE16" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC16" s="4" t="inlineStr">
+      <c r="AF16" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AD16" s="4" t="inlineStr"/>
-      <c r="AE16" s="4" t="inlineStr"/>
-      <c r="AF16" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG16" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG16" s="4" t="inlineStr"/>
+      <c r="AH16" s="4" t="inlineStr"/>
+      <c r="AI16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -2405,82 +2498,87 @@
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="L17" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="4" t="n">
+      <c r="M17" s="4" t="inlineStr"/>
+      <c r="N17" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M17" s="4" t="n">
+      <c r="O17" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O17" s="4" t="n">
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="n">
         <v>1438.5</v>
       </c>
-      <c r="P17" s="4" t="n">
+      <c r="R17" s="4" t="n">
         <v>1438.5</v>
       </c>
-      <c r="Q17" s="4" t="n">
+      <c r="S17" s="4" t="n">
         <v>1424.12</v>
       </c>
-      <c r="R17" s="4" t="n">
+      <c r="T17" s="4" t="n">
         <v>1452.88</v>
       </c>
-      <c r="S17" s="4" t="n">
+      <c r="U17" s="4" t="n">
         <v>1366.575</v>
       </c>
-      <c r="T17" s="4" t="n">
+      <c r="V17" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U17" s="4" t="n">
+      <c r="W17" s="4" t="n">
         <v>1515</v>
       </c>
-      <c r="V17" s="4" t="n">
+      <c r="X17" s="4" t="n">
         <v>5.32</v>
       </c>
-      <c r="W17" s="4" t="n">
+      <c r="Y17" s="4" t="n">
         <v>1654.275</v>
       </c>
-      <c r="X17" s="4" t="n">
+      <c r="Z17" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="4" t="inlineStr"/>
-      <c r="AA17" s="4" t="inlineStr"/>
-      <c r="AB17" s="4" t="inlineStr">
+      <c r="AA17" s="4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="4" t="inlineStr"/>
+      <c r="AD17" s="4" t="inlineStr"/>
+      <c r="AE17" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC17" s="4" t="inlineStr"/>
-      <c r="AD17" s="4" t="inlineStr">
+      <c r="AF17" s="4" t="inlineStr"/>
+      <c r="AG17" s="4" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="AE17" s="4" t="inlineStr"/>
-      <c r="AF17" s="4" t="n">
+      <c r="AH17" s="4" t="inlineStr"/>
+      <c r="AI17" s="4" t="n">
         <v>5.32</v>
       </c>
-      <c r="AG17" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -2516,82 +2614,87 @@
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr"/>
+      <c r="J18" s="4" t="n">
         <v>89</v>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n">
+      <c r="L18" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="4" t="n">
+      <c r="M18" s="4" t="inlineStr"/>
+      <c r="N18" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M18" s="4" t="n">
+      <c r="O18" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="n">
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="n">
         <v>2014.8</v>
       </c>
-      <c r="P18" s="4" t="n">
+      <c r="R18" s="4" t="n">
         <v>2014.8</v>
       </c>
-      <c r="Q18" s="4" t="n">
+      <c r="S18" s="4" t="n">
         <v>1994.65</v>
       </c>
-      <c r="R18" s="4" t="n">
+      <c r="T18" s="4" t="n">
         <v>2034.95</v>
       </c>
-      <c r="S18" s="4" t="n">
+      <c r="U18" s="4" t="n">
         <v>1914.06</v>
       </c>
-      <c r="T18" s="4" t="n">
+      <c r="V18" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U18" s="4" t="n">
+      <c r="W18" s="4" t="n">
         <v>2107</v>
       </c>
-      <c r="V18" s="4" t="n">
+      <c r="X18" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="W18" s="4" t="n">
+      <c r="Y18" s="4" t="n">
         <v>2317.02</v>
       </c>
-      <c r="X18" s="4" t="n">
+      <c r="Z18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="4" t="inlineStr"/>
-      <c r="AA18" s="4" t="inlineStr"/>
-      <c r="AB18" s="4" t="inlineStr">
+      <c r="AA18" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="4" t="inlineStr"/>
+      <c r="AD18" s="4" t="inlineStr"/>
+      <c r="AE18" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC18" s="4" t="inlineStr"/>
-      <c r="AD18" s="4" t="inlineStr">
+      <c r="AF18" s="4" t="inlineStr"/>
+      <c r="AG18" s="4" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="AE18" s="4" t="inlineStr"/>
-      <c r="AF18" s="4" t="n">
+      <c r="AH18" s="4" t="inlineStr"/>
+      <c r="AI18" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="AG18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -2627,82 +2730,87 @@
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="L19" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4" t="n">
+      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M19" s="4" t="n">
+      <c r="O19" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="n">
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="n">
         <v>2417</v>
       </c>
-      <c r="P19" s="4" t="n">
+      <c r="R19" s="4" t="n">
         <v>2417</v>
       </c>
-      <c r="Q19" s="4" t="n">
+      <c r="S19" s="4" t="n">
         <v>2392.83</v>
       </c>
-      <c r="R19" s="4" t="n">
+      <c r="T19" s="4" t="n">
         <v>2441.17</v>
       </c>
-      <c r="S19" s="4" t="n">
+      <c r="U19" s="4" t="n">
         <v>2296.15</v>
       </c>
-      <c r="T19" s="4" t="n">
+      <c r="V19" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U19" s="4" t="n">
+      <c r="W19" s="4" t="n">
         <v>2610.36</v>
       </c>
-      <c r="V19" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W19" s="4" t="n">
+      <c r="X19" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y19" s="4" t="n">
         <v>2779.55</v>
       </c>
-      <c r="X19" s="4" t="n">
+      <c r="Z19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="4" t="inlineStr"/>
-      <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="inlineStr">
+      <c r="AA19" s="4" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="AB19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="4" t="inlineStr"/>
+      <c r="AD19" s="4" t="inlineStr"/>
+      <c r="AE19" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC19" s="4" t="inlineStr"/>
-      <c r="AD19" s="4" t="inlineStr">
+      <c r="AF19" s="4" t="inlineStr"/>
+      <c r="AG19" s="4" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="AE19" s="4" t="inlineStr"/>
-      <c r="AF19" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG19" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AH19" s="4" t="inlineStr"/>
+      <c r="AI19" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -2738,82 +2846,87 @@
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J20" s="4" t="n">
+      <c r="L20" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="4" t="n">
+      <c r="M20" s="4" t="inlineStr"/>
+      <c r="N20" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M20" s="4" t="n">
+      <c r="O20" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="n">
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="n">
         <v>1625.5</v>
       </c>
-      <c r="P20" s="4" t="n">
+      <c r="R20" s="4" t="n">
         <v>1625.5</v>
       </c>
-      <c r="Q20" s="4" t="n">
+      <c r="S20" s="4" t="n">
         <v>1609.24</v>
       </c>
-      <c r="R20" s="4" t="n">
+      <c r="T20" s="4" t="n">
         <v>1641.76</v>
       </c>
-      <c r="S20" s="4" t="n">
+      <c r="U20" s="4" t="n">
         <v>1544.225</v>
       </c>
-      <c r="T20" s="4" t="n">
+      <c r="V20" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U20" s="4" t="n">
+      <c r="W20" s="4" t="n">
         <v>1648</v>
       </c>
-      <c r="V20" s="4" t="n">
+      <c r="X20" s="4" t="n">
         <v>1.38</v>
       </c>
-      <c r="W20" s="4" t="n">
+      <c r="Y20" s="4" t="n">
         <v>1869.325</v>
       </c>
-      <c r="X20" s="4" t="n">
+      <c r="Z20" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="4" t="inlineStr"/>
-      <c r="AA20" s="4" t="inlineStr"/>
-      <c r="AB20" s="4" t="inlineStr">
+      <c r="AA20" s="4" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="AB20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="4" t="inlineStr"/>
+      <c r="AD20" s="4" t="inlineStr"/>
+      <c r="AE20" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC20" s="4" t="inlineStr"/>
-      <c r="AD20" s="4" t="inlineStr">
+      <c r="AF20" s="4" t="inlineStr"/>
+      <c r="AG20" s="4" t="inlineStr">
         <is>
           <t>Chemicals</t>
         </is>
       </c>
-      <c r="AE20" s="4" t="inlineStr"/>
-      <c r="AF20" s="4" t="n">
+      <c r="AH20" s="4" t="inlineStr"/>
+      <c r="AI20" s="4" t="n">
         <v>1.38</v>
       </c>
-      <c r="AG20" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -2849,82 +2962,87 @@
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="L21" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="K21" s="4" t="inlineStr"/>
-      <c r="L21" s="4" t="n">
+      <c r="M21" s="4" t="inlineStr"/>
+      <c r="N21" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M21" s="4" t="n">
+      <c r="O21" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="n">
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="n">
         <v>345.8</v>
       </c>
-      <c r="P21" s="4" t="n">
+      <c r="R21" s="4" t="n">
         <v>345.8</v>
       </c>
-      <c r="Q21" s="4" t="n">
+      <c r="S21" s="4" t="n">
         <v>342.34</v>
       </c>
-      <c r="R21" s="4" t="n">
+      <c r="T21" s="4" t="n">
         <v>349.26</v>
       </c>
-      <c r="S21" s="4" t="n">
+      <c r="U21" s="4" t="n">
         <v>328.51</v>
       </c>
-      <c r="T21" s="4" t="n">
+      <c r="V21" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U21" s="4" t="n">
+      <c r="W21" s="4" t="n">
         <v>373.4640000000001</v>
       </c>
-      <c r="V21" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W21" s="4" t="n">
+      <c r="X21" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y21" s="4" t="n">
         <v>397.67</v>
       </c>
-      <c r="X21" s="4" t="n">
+      <c r="Z21" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="4" t="inlineStr"/>
-      <c r="AA21" s="4" t="inlineStr"/>
-      <c r="AB21" s="4" t="inlineStr">
+      <c r="AA21" s="4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AB21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="4" t="inlineStr"/>
+      <c r="AD21" s="4" t="inlineStr"/>
+      <c r="AE21" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC21" s="4" t="inlineStr"/>
-      <c r="AD21" s="4" t="inlineStr">
+      <c r="AF21" s="4" t="inlineStr"/>
+      <c r="AG21" s="4" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="AE21" s="4" t="inlineStr"/>
-      <c r="AF21" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AH21" s="4" t="inlineStr"/>
+      <c r="AI21" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -2960,82 +3078,87 @@
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="n">
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J22" s="4" t="n">
+      <c r="L22" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="4" t="n">
+      <c r="M22" s="4" t="inlineStr"/>
+      <c r="N22" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M22" s="4" t="n">
+      <c r="O22" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="n">
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="n">
         <v>389.3</v>
       </c>
-      <c r="P22" s="4" t="n">
+      <c r="R22" s="4" t="n">
         <v>389.3</v>
       </c>
-      <c r="Q22" s="4" t="n">
+      <c r="S22" s="4" t="n">
         <v>385.41</v>
       </c>
-      <c r="R22" s="4" t="n">
+      <c r="T22" s="4" t="n">
         <v>393.19</v>
       </c>
-      <c r="S22" s="4" t="n">
+      <c r="U22" s="4" t="n">
         <v>369.835</v>
       </c>
-      <c r="T22" s="4" t="n">
+      <c r="V22" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U22" s="4" t="n">
+      <c r="W22" s="4" t="n">
         <v>420.444</v>
       </c>
-      <c r="V22" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W22" s="4" t="n">
+      <c r="X22" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y22" s="4" t="n">
         <v>447.695</v>
       </c>
-      <c r="X22" s="4" t="n">
+      <c r="Z22" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="4" t="inlineStr"/>
-      <c r="AA22" s="4" t="inlineStr"/>
-      <c r="AB22" s="4" t="inlineStr">
+      <c r="AA22" s="4" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="AB22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="4" t="inlineStr"/>
+      <c r="AD22" s="4" t="inlineStr"/>
+      <c r="AE22" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC22" s="4" t="inlineStr"/>
-      <c r="AD22" s="4" t="inlineStr">
+      <c r="AF22" s="4" t="inlineStr"/>
+      <c r="AG22" s="4" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="AE22" s="4" t="inlineStr"/>
-      <c r="AF22" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AH22" s="4" t="inlineStr"/>
+      <c r="AI22" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -3071,82 +3194,87 @@
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
+      <c r="J23" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="L23" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="4" t="n">
+      <c r="M23" s="4" t="inlineStr"/>
+      <c r="N23" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M23" s="4" t="n">
+      <c r="O23" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O23" s="4" t="n">
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="n">
         <v>285.9</v>
       </c>
-      <c r="P23" s="4" t="n">
+      <c r="R23" s="4" t="n">
         <v>285.9</v>
       </c>
-      <c r="Q23" s="4" t="n">
+      <c r="S23" s="4" t="n">
         <v>283.04</v>
       </c>
-      <c r="R23" s="4" t="n">
+      <c r="T23" s="4" t="n">
         <v>288.76</v>
       </c>
-      <c r="S23" s="4" t="n">
+      <c r="U23" s="4" t="n">
         <v>271.605</v>
       </c>
-      <c r="T23" s="4" t="n">
+      <c r="V23" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U23" s="4" t="n">
+      <c r="W23" s="4" t="n">
         <v>308.772</v>
       </c>
-      <c r="V23" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W23" s="4" t="n">
+      <c r="X23" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y23" s="4" t="n">
         <v>328.785</v>
       </c>
-      <c r="X23" s="4" t="n">
+      <c r="Z23" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="4" t="inlineStr"/>
-      <c r="AA23" s="4" t="inlineStr"/>
-      <c r="AB23" s="4" t="inlineStr">
+      <c r="AA23" s="4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AD23" s="4" t="inlineStr"/>
+      <c r="AE23" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC23" s="4" t="inlineStr"/>
-      <c r="AD23" s="4" t="inlineStr">
+      <c r="AF23" s="4" t="inlineStr"/>
+      <c r="AG23" s="4" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="AE23" s="4" t="inlineStr"/>
-      <c r="AF23" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG23" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AH23" s="4" t="inlineStr"/>
+      <c r="AI23" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -3182,82 +3310,87 @@
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="4" t="n">
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J24" s="4" t="n">
+      <c r="L24" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="4" t="n">
+      <c r="M24" s="4" t="inlineStr"/>
+      <c r="N24" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M24" s="4" t="n">
+      <c r="O24" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O24" s="4" t="n">
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="n">
         <v>494.4</v>
       </c>
-      <c r="P24" s="4" t="n">
+      <c r="R24" s="4" t="n">
         <v>494.4</v>
       </c>
-      <c r="Q24" s="4" t="n">
+      <c r="S24" s="4" t="n">
         <v>489.46</v>
       </c>
-      <c r="R24" s="4" t="n">
+      <c r="T24" s="4" t="n">
         <v>499.34</v>
       </c>
-      <c r="S24" s="4" t="n">
+      <c r="U24" s="4" t="n">
         <v>469.6799999999999</v>
       </c>
-      <c r="T24" s="4" t="n">
+      <c r="V24" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U24" s="4" t="n">
+      <c r="W24" s="4" t="n">
         <v>533.952</v>
       </c>
-      <c r="V24" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W24" s="4" t="n">
+      <c r="X24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y24" s="4" t="n">
         <v>568.5599999999999</v>
       </c>
-      <c r="X24" s="4" t="n">
+      <c r="Z24" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="4" t="inlineStr"/>
-      <c r="AA24" s="4" t="inlineStr"/>
-      <c r="AB24" s="4" t="inlineStr">
+      <c r="AA24" s="4" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="AB24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="4" t="inlineStr"/>
+      <c r="AD24" s="4" t="inlineStr"/>
+      <c r="AE24" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC24" s="4" t="inlineStr"/>
-      <c r="AD24" s="4" t="inlineStr">
+      <c r="AF24" s="4" t="inlineStr"/>
+      <c r="AG24" s="4" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="AE24" s="4" t="inlineStr"/>
-      <c r="AF24" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG24" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AH24" s="4" t="inlineStr"/>
+      <c r="AI24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -3293,82 +3426,87 @@
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr"/>
+      <c r="J25" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="L25" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="K25" s="4" t="inlineStr"/>
-      <c r="L25" s="4" t="n">
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M25" s="4" t="n">
+      <c r="O25" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O25" s="4" t="n">
+      <c r="P25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="n">
         <v>388.7</v>
       </c>
-      <c r="P25" s="4" t="n">
+      <c r="R25" s="4" t="n">
         <v>388.7</v>
       </c>
-      <c r="Q25" s="4" t="n">
+      <c r="S25" s="4" t="n">
         <v>384.81</v>
       </c>
-      <c r="R25" s="4" t="n">
+      <c r="T25" s="4" t="n">
         <v>392.59</v>
       </c>
-      <c r="S25" s="4" t="n">
+      <c r="U25" s="4" t="n">
         <v>369.265</v>
       </c>
-      <c r="T25" s="4" t="n">
+      <c r="V25" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U25" s="4" t="n">
+      <c r="W25" s="4" t="n">
         <v>419.796</v>
       </c>
-      <c r="V25" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W25" s="4" t="n">
+      <c r="X25" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y25" s="4" t="n">
         <v>447.0049999999999</v>
       </c>
-      <c r="X25" s="4" t="n">
+      <c r="Z25" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="4" t="inlineStr"/>
-      <c r="AA25" s="4" t="inlineStr"/>
-      <c r="AB25" s="4" t="inlineStr">
+      <c r="AA25" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AD25" s="4" t="inlineStr"/>
+      <c r="AE25" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC25" s="4" t="inlineStr"/>
-      <c r="AD25" s="4" t="inlineStr">
+      <c r="AF25" s="4" t="inlineStr"/>
+      <c r="AG25" s="4" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="AE25" s="4" t="inlineStr"/>
-      <c r="AF25" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AH25" s="4" t="inlineStr"/>
+      <c r="AI25" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -3404,82 +3542,87 @@
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="4" t="n">
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr"/>
+      <c r="J26" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n">
+      <c r="L26" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="4" t="n">
+      <c r="M26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M26" s="4" t="n">
+      <c r="O26" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O26" s="4" t="n">
+      <c r="P26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="n">
         <v>411.3</v>
       </c>
-      <c r="P26" s="4" t="n">
+      <c r="R26" s="4" t="n">
         <v>411.3</v>
       </c>
-      <c r="Q26" s="4" t="n">
+      <c r="S26" s="4" t="n">
         <v>407.19</v>
       </c>
-      <c r="R26" s="4" t="n">
+      <c r="T26" s="4" t="n">
         <v>415.41</v>
       </c>
-      <c r="S26" s="4" t="n">
+      <c r="U26" s="4" t="n">
         <v>390.735</v>
       </c>
-      <c r="T26" s="4" t="n">
+      <c r="V26" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U26" s="4" t="n">
+      <c r="W26" s="4" t="n">
         <v>444.2040000000001</v>
       </c>
-      <c r="V26" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W26" s="4" t="n">
+      <c r="X26" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y26" s="4" t="n">
         <v>472.995</v>
       </c>
-      <c r="X26" s="4" t="n">
+      <c r="Z26" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="4" t="inlineStr"/>
-      <c r="AA26" s="4" t="inlineStr"/>
-      <c r="AB26" s="4" t="inlineStr">
+      <c r="AA26" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="4" t="inlineStr"/>
+      <c r="AD26" s="4" t="inlineStr"/>
+      <c r="AE26" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC26" s="4" t="inlineStr"/>
-      <c r="AD26" s="4" t="inlineStr">
+      <c r="AF26" s="4" t="inlineStr"/>
+      <c r="AG26" s="4" t="inlineStr">
         <is>
           <t>Metal</t>
         </is>
       </c>
-      <c r="AE26" s="4" t="inlineStr"/>
-      <c r="AF26" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG26" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AH26" s="4" t="inlineStr"/>
+      <c r="AI26" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -3511,82 +3654,87 @@
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="4" t="n">
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr"/>
+      <c r="J27" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n">
+      <c r="L27" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="K27" s="4" t="inlineStr"/>
-      <c r="L27" s="4" t="n">
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M27" s="4" t="n">
+      <c r="O27" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O27" s="4" t="n">
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="n">
         <v>5406</v>
       </c>
-      <c r="P27" s="4" t="n">
+      <c r="R27" s="4" t="n">
         <v>5406</v>
       </c>
-      <c r="Q27" s="4" t="n">
+      <c r="S27" s="4" t="n">
         <v>5351.94</v>
       </c>
-      <c r="R27" s="4" t="n">
+      <c r="T27" s="4" t="n">
         <v>5460.06</v>
       </c>
-      <c r="S27" s="4" t="n">
+      <c r="U27" s="4" t="n">
         <v>5135.7</v>
       </c>
-      <c r="T27" s="4" t="n">
+      <c r="V27" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U27" s="4" t="n">
+      <c r="W27" s="4" t="n">
         <v>5838.48</v>
       </c>
-      <c r="V27" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W27" s="4" t="n">
+      <c r="X27" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y27" s="4" t="n">
         <v>6216.9</v>
       </c>
-      <c r="X27" s="4" t="n">
+      <c r="Z27" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="4" t="inlineStr"/>
-      <c r="AA27" s="4" t="inlineStr"/>
-      <c r="AB27" s="4" t="inlineStr">
+      <c r="AA27" s="4" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="AB27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="4" t="inlineStr"/>
+      <c r="AD27" s="4" t="inlineStr"/>
+      <c r="AE27" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC27" s="4" t="inlineStr"/>
-      <c r="AD27" s="4" t="inlineStr">
+      <c r="AF27" s="4" t="inlineStr"/>
+      <c r="AG27" s="4" t="inlineStr">
         <is>
           <t>FMCG</t>
         </is>
       </c>
-      <c r="AE27" s="4" t="inlineStr"/>
-      <c r="AF27" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AH27" s="4" t="inlineStr"/>
+      <c r="AI27" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -3621,93 +3769,96 @@
           <t>NEW BUY</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="J28" s="4" t="n">
         <v>56.8</v>
       </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J28" s="4" t="n">
+      <c r="L28" s="4" t="n">
         <v>29.2</v>
       </c>
-      <c r="K28" s="4" t="n">
+      <c r="M28" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="N28" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="M28" s="4" t="n">
+      <c r="O28" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O28" s="4" t="n">
+      <c r="Q28" s="4" t="n">
         <v>368.98</v>
       </c>
-      <c r="P28" s="4" t="n">
+      <c r="R28" s="4" t="n">
         <v>368.98</v>
       </c>
-      <c r="Q28" s="4" t="n">
+      <c r="S28" s="4" t="n">
         <v>365.29</v>
       </c>
-      <c r="R28" s="4" t="n">
+      <c r="T28" s="4" t="n">
         <v>372.67</v>
       </c>
-      <c r="S28" s="4" t="n">
+      <c r="U28" s="4" t="n">
         <v>346.84</v>
       </c>
-      <c r="T28" s="4" t="n">
+      <c r="V28" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="U28" s="4" t="n">
+      <c r="W28" s="4" t="n">
         <v>413.26</v>
       </c>
-      <c r="V28" s="4" t="n">
+      <c r="X28" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="W28" s="4" t="n">
+      <c r="Y28" s="4" t="n">
         <v>457.54</v>
       </c>
-      <c r="X28" s="4" t="n">
+      <c r="Z28" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="Y28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="4" t="n">
+      <c r="AA28" s="4" t="inlineStr"/>
+      <c r="AB28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="4" t="n">
         <v>1.46</v>
       </c>
-      <c r="AA28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="4" t="inlineStr">
+      <c r="AD28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC28" s="4" t="inlineStr">
+      <c r="AF28" s="4" t="inlineStr">
         <is>
           <t>Momentum · Value · Trend</t>
         </is>
       </c>
-      <c r="AD28" s="4" t="inlineStr"/>
-      <c r="AE28" s="4" t="n">
+      <c r="AG28" s="4" t="inlineStr"/>
+      <c r="AH28" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AF28" s="4" t="n">
+      <c r="AI28" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AG28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -3742,91 +3893,94 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="J29" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n">
+      <c r="L29" s="4" t="n">
         <v>27.8</v>
       </c>
-      <c r="K29" s="4" t="n">
+      <c r="M29" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="N29" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="M29" s="4" t="n">
+      <c r="O29" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="P29" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O29" s="4" t="n">
+      <c r="Q29" s="4" t="n">
         <v>358.56</v>
       </c>
-      <c r="P29" s="4" t="n">
+      <c r="R29" s="4" t="n">
         <v>358.56</v>
       </c>
-      <c r="Q29" s="4" t="n">
+      <c r="S29" s="4" t="n">
         <v>354.97</v>
       </c>
-      <c r="R29" s="4" t="n">
+      <c r="T29" s="4" t="n">
         <v>362.15</v>
       </c>
-      <c r="S29" s="4" t="n">
+      <c r="U29" s="4" t="n">
         <v>340.63</v>
       </c>
-      <c r="T29" s="4" t="n">
+      <c r="V29" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U29" s="4" t="n">
+      <c r="W29" s="4" t="n">
         <v>387.24</v>
       </c>
-      <c r="V29" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W29" s="4" t="n">
+      <c r="X29" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="4" t="n">
         <v>412.34</v>
       </c>
-      <c r="X29" s="4" t="n">
+      <c r="Z29" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="4" t="n">
+      <c r="AA29" s="4" t="inlineStr"/>
+      <c r="AB29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="4" t="n">
         <v>2.11</v>
       </c>
-      <c r="AA29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="4" t="inlineStr">
+      <c r="AD29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC29" s="4" t="inlineStr">
+      <c r="AF29" s="4" t="inlineStr">
         <is>
           <t>Momentum · Trend · Quality</t>
         </is>
       </c>
-      <c r="AD29" s="4" t="inlineStr"/>
-      <c r="AE29" s="4" t="inlineStr"/>
-      <c r="AF29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG29" s="4" t="inlineStr"/>
+      <c r="AH29" s="4" t="inlineStr"/>
+      <c r="AI29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -3858,94 +4012,103 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+12.2pp)</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="J30" s="4" t="n">
         <v>47.3</v>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n">
+      <c r="L30" s="4" t="n">
         <v>17.1</v>
       </c>
-      <c r="K30" s="4" t="n">
+      <c r="M30" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="N30" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M30" s="4" t="n">
+      <c r="O30" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="P30" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O30" s="4" t="n">
+      <c r="Q30" s="4" t="n">
         <v>202.81</v>
       </c>
-      <c r="P30" s="4" t="n">
+      <c r="R30" s="4" t="n">
         <v>202.81</v>
       </c>
-      <c r="Q30" s="4" t="n">
+      <c r="S30" s="4" t="n">
         <v>200.78</v>
       </c>
-      <c r="R30" s="4" t="n">
+      <c r="T30" s="4" t="n">
         <v>204.84</v>
       </c>
-      <c r="S30" s="4" t="n">
+      <c r="U30" s="4" t="n">
         <v>192.67</v>
       </c>
-      <c r="T30" s="4" t="n">
+      <c r="V30" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U30" s="4" t="n">
+      <c r="W30" s="4" t="n">
         <v>219.03</v>
       </c>
-      <c r="V30" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W30" s="4" t="n">
+      <c r="X30" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y30" s="4" t="n">
         <v>233.23</v>
       </c>
-      <c r="X30" s="4" t="n">
+      <c r="Z30" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="4" t="n">
+      <c r="AA30" s="4" t="inlineStr"/>
+      <c r="AB30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="4" t="n">
         <v>-1.02</v>
       </c>
-      <c r="AB30" s="4" t="inlineStr">
+      <c r="AE30" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC30" s="4" t="inlineStr">
+      <c r="AF30" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · Mean Reversion</t>
         </is>
       </c>
-      <c r="AD30" s="4" t="inlineStr"/>
-      <c r="AE30" s="4" t="inlineStr"/>
-      <c r="AF30" s="4" t="n">
+      <c r="AG30" s="4" t="inlineStr"/>
+      <c r="AH30" s="4" t="inlineStr"/>
+      <c r="AI30" s="4" t="n">
         <v>12.15</v>
       </c>
-      <c r="AG30" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -3977,94 +4140,103 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+13.0pp)</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="J31" s="4" t="n">
         <v>49.7</v>
       </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
+      <c r="L31" s="4" t="n">
         <v>16.3</v>
       </c>
-      <c r="K31" s="4" t="n">
+      <c r="M31" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="N31" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M31" s="4" t="n">
+      <c r="O31" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O31" s="4" t="n">
+      <c r="Q31" s="4" t="n">
         <v>341.1</v>
       </c>
-      <c r="P31" s="4" t="n">
+      <c r="R31" s="4" t="n">
         <v>341.1</v>
       </c>
-      <c r="Q31" s="4" t="n">
+      <c r="S31" s="4" t="n">
         <v>337.69</v>
       </c>
-      <c r="R31" s="4" t="n">
+      <c r="T31" s="4" t="n">
         <v>344.51</v>
       </c>
-      <c r="S31" s="4" t="n">
+      <c r="U31" s="4" t="n">
         <v>324.05</v>
       </c>
-      <c r="T31" s="4" t="n">
+      <c r="V31" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U31" s="4" t="n">
+      <c r="W31" s="4" t="n">
         <v>368.39</v>
       </c>
-      <c r="V31" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W31" s="4" t="n">
+      <c r="X31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y31" s="4" t="n">
         <v>392.26</v>
       </c>
-      <c r="X31" s="4" t="n">
+      <c r="Z31" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="4" t="n">
+      <c r="AA31" s="4" t="inlineStr"/>
+      <c r="AB31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="4" t="n">
         <v>3.13</v>
       </c>
-      <c r="AA31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" s="4" t="inlineStr">
+      <c r="AD31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC31" s="4" t="inlineStr">
+      <c r="AF31" s="4" t="inlineStr">
         <is>
           <t>Momentum · Value · Mean Reversion</t>
         </is>
       </c>
-      <c r="AD31" s="4" t="inlineStr"/>
-      <c r="AE31" s="4" t="inlineStr"/>
-      <c r="AF31" s="4" t="n">
+      <c r="AG31" s="4" t="inlineStr"/>
+      <c r="AH31" s="4" t="inlineStr"/>
+      <c r="AI31" s="4" t="n">
         <v>12.97</v>
       </c>
-      <c r="AG31" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ31" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -4096,94 +4268,103 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+14.4pp)</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="J32" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J32" s="4" t="n">
+      <c r="L32" s="4" t="n">
         <v>14.8</v>
       </c>
-      <c r="K32" s="4" t="n">
+      <c r="M32" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L32" s="4" t="n">
+      <c r="N32" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M32" s="4" t="n">
+      <c r="O32" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="P32" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O32" s="4" t="n">
+      <c r="Q32" s="4" t="n">
         <v>225.02</v>
       </c>
-      <c r="P32" s="4" t="n">
+      <c r="R32" s="4" t="n">
         <v>225.02</v>
       </c>
-      <c r="Q32" s="4" t="n">
+      <c r="S32" s="4" t="n">
         <v>222.77</v>
       </c>
-      <c r="R32" s="4" t="n">
+      <c r="T32" s="4" t="n">
         <v>227.27</v>
       </c>
-      <c r="S32" s="4" t="n">
+      <c r="U32" s="4" t="n">
         <v>213.77</v>
       </c>
-      <c r="T32" s="4" t="n">
+      <c r="V32" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U32" s="4" t="n">
+      <c r="W32" s="4" t="n">
         <v>243.02</v>
       </c>
-      <c r="V32" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W32" s="4" t="n">
+      <c r="X32" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y32" s="4" t="n">
         <v>258.77</v>
       </c>
-      <c r="X32" s="4" t="n">
+      <c r="Z32" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="4" t="n">
+      <c r="AA32" s="4" t="inlineStr"/>
+      <c r="AB32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="4" t="n">
         <v>8.01</v>
       </c>
-      <c r="AA32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="4" t="inlineStr">
+      <c r="AD32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC32" s="4" t="inlineStr">
+      <c r="AF32" s="4" t="inlineStr">
         <is>
           <t>Mean Reversion · Growth · Value</t>
         </is>
       </c>
-      <c r="AD32" s="4" t="inlineStr"/>
-      <c r="AE32" s="4" t="inlineStr"/>
-      <c r="AF32" s="4" t="n">
+      <c r="AG32" s="4" t="inlineStr"/>
+      <c r="AH32" s="4" t="inlineStr"/>
+      <c r="AI32" s="4" t="n">
         <v>14.45</v>
       </c>
-      <c r="AG32" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ32" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -4215,94 +4396,103 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+14.8pp)</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="J33" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n">
+      <c r="L33" s="4" t="n">
         <v>14.5</v>
       </c>
-      <c r="K33" s="4" t="n">
+      <c r="M33" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L33" s="4" t="n">
+      <c r="N33" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M33" s="4" t="n">
+      <c r="O33" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="P33" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O33" s="4" t="n">
+      <c r="Q33" s="4" t="n">
         <v>1065.22</v>
       </c>
-      <c r="P33" s="4" t="n">
+      <c r="R33" s="4" t="n">
         <v>1065.22</v>
       </c>
-      <c r="Q33" s="4" t="n">
+      <c r="S33" s="4" t="n">
         <v>1054.57</v>
       </c>
-      <c r="R33" s="4" t="n">
+      <c r="T33" s="4" t="n">
         <v>1075.87</v>
       </c>
-      <c r="S33" s="4" t="n">
+      <c r="U33" s="4" t="n">
         <v>1011.96</v>
       </c>
-      <c r="T33" s="4" t="n">
+      <c r="V33" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U33" s="4" t="n">
+      <c r="W33" s="4" t="n">
         <v>1150.44</v>
       </c>
-      <c r="V33" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W33" s="4" t="n">
+      <c r="X33" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y33" s="4" t="n">
         <v>1225</v>
       </c>
-      <c r="X33" s="4" t="n">
+      <c r="Z33" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="4" t="n">
+      <c r="AA33" s="4" t="inlineStr"/>
+      <c r="AB33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="4" t="n">
         <v>-4.4</v>
       </c>
-      <c r="AB33" s="4" t="inlineStr">
+      <c r="AE33" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC33" s="4" t="inlineStr">
+      <c r="AF33" s="4" t="inlineStr">
         <is>
           <t>Value · News · Event Driven</t>
         </is>
       </c>
-      <c r="AD33" s="4" t="inlineStr"/>
-      <c r="AE33" s="4" t="inlineStr"/>
-      <c r="AF33" s="4" t="n">
+      <c r="AG33" s="4" t="inlineStr"/>
+      <c r="AH33" s="4" t="inlineStr"/>
+      <c r="AI33" s="4" t="n">
         <v>14.77</v>
       </c>
-      <c r="AG33" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ33" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -4334,94 +4524,103 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+14.9pp)</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="J34" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J34" s="4" t="n">
+      <c r="L34" s="4" t="n">
         <v>14.4</v>
       </c>
-      <c r="K34" s="4" t="n">
+      <c r="M34" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="4" t="n">
+      <c r="N34" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M34" s="4" t="n">
+      <c r="O34" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="P34" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O34" s="4" t="n">
+      <c r="Q34" s="4" t="n">
         <v>333.74</v>
       </c>
-      <c r="P34" s="4" t="n">
+      <c r="R34" s="4" t="n">
         <v>333.74</v>
       </c>
-      <c r="Q34" s="4" t="n">
+      <c r="S34" s="4" t="n">
         <v>330.4</v>
       </c>
-      <c r="R34" s="4" t="n">
+      <c r="T34" s="4" t="n">
         <v>337.08</v>
       </c>
-      <c r="S34" s="4" t="n">
+      <c r="U34" s="4" t="n">
         <v>317.05</v>
       </c>
-      <c r="T34" s="4" t="n">
+      <c r="V34" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U34" s="4" t="n">
+      <c r="W34" s="4" t="n">
         <v>360.44</v>
       </c>
-      <c r="V34" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W34" s="4" t="n">
+      <c r="X34" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y34" s="4" t="n">
         <v>383.8</v>
       </c>
-      <c r="X34" s="4" t="n">
+      <c r="Z34" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="4" t="n">
+      <c r="AA34" s="4" t="inlineStr"/>
+      <c r="AB34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="4" t="n">
         <v>-7.44</v>
       </c>
-      <c r="AB34" s="4" t="inlineStr">
+      <c r="AE34" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC34" s="4" t="inlineStr">
+      <c r="AF34" s="4" t="inlineStr">
         <is>
           <t>Value · Trend · Momentum</t>
         </is>
       </c>
-      <c r="AD34" s="4" t="inlineStr"/>
-      <c r="AE34" s="4" t="inlineStr"/>
-      <c r="AF34" s="4" t="n">
+      <c r="AG34" s="4" t="inlineStr"/>
+      <c r="AH34" s="4" t="inlineStr"/>
+      <c r="AI34" s="4" t="n">
         <v>14.87</v>
       </c>
-      <c r="AG34" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ34" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -4453,94 +4652,103 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>8</v>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+15.2pp)</t>
+        </is>
       </c>
       <c r="H35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J35" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J35" s="4" t="n">
+      <c r="L35" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="K35" s="4" t="n">
+      <c r="M35" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L35" s="4" t="n">
+      <c r="N35" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M35" s="4" t="n">
+      <c r="O35" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="P35" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="O35" s="4" t="n">
+      <c r="Q35" s="4" t="n">
         <v>393.82</v>
       </c>
-      <c r="P35" s="4" t="n">
+      <c r="R35" s="4" t="n">
         <v>393.82</v>
       </c>
-      <c r="Q35" s="4" t="n">
+      <c r="S35" s="4" t="n">
         <v>389.88</v>
       </c>
-      <c r="R35" s="4" t="n">
+      <c r="T35" s="4" t="n">
         <v>397.76</v>
       </c>
-      <c r="S35" s="4" t="n">
+      <c r="U35" s="4" t="n">
         <v>374.13</v>
       </c>
-      <c r="T35" s="4" t="n">
+      <c r="V35" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U35" s="4" t="n">
+      <c r="W35" s="4" t="n">
         <v>425.33</v>
       </c>
-      <c r="V35" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W35" s="4" t="n">
+      <c r="X35" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y35" s="4" t="n">
         <v>452.89</v>
       </c>
-      <c r="X35" s="4" t="n">
+      <c r="Z35" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="4" t="n">
+      <c r="AA35" s="4" t="inlineStr"/>
+      <c r="AB35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="AA35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="4" t="inlineStr">
+      <c r="AD35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC35" s="4" t="inlineStr">
+      <c r="AF35" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Trend</t>
         </is>
       </c>
-      <c r="AD35" s="4" t="inlineStr"/>
-      <c r="AE35" s="4" t="inlineStr"/>
-      <c r="AF35" s="4" t="n">
+      <c r="AG35" s="4" t="inlineStr"/>
+      <c r="AH35" s="4" t="inlineStr"/>
+      <c r="AI35" s="4" t="n">
         <v>15.21</v>
       </c>
-      <c r="AG35" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ35" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -4572,94 +4780,103 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+15.5pp)</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="J36" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J36" s="4" t="n">
+      <c r="L36" s="4" t="n">
         <v>13.8</v>
       </c>
-      <c r="K36" s="4" t="n">
+      <c r="M36" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L36" s="4" t="n">
+      <c r="N36" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M36" s="4" t="n">
+      <c r="O36" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="P36" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O36" s="4" t="n">
+      <c r="Q36" s="4" t="n">
         <v>81.56</v>
       </c>
-      <c r="P36" s="4" t="n">
+      <c r="R36" s="4" t="n">
         <v>81.56</v>
       </c>
-      <c r="Q36" s="4" t="n">
+      <c r="S36" s="4" t="n">
         <v>80.73999999999999</v>
       </c>
-      <c r="R36" s="4" t="n">
+      <c r="T36" s="4" t="n">
         <v>82.38</v>
       </c>
-      <c r="S36" s="4" t="n">
+      <c r="U36" s="4" t="n">
         <v>77.48</v>
       </c>
-      <c r="T36" s="4" t="n">
+      <c r="V36" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U36" s="4" t="n">
+      <c r="W36" s="4" t="n">
         <v>88.08</v>
       </c>
-      <c r="V36" s="4" t="n">
+      <c r="X36" s="4" t="n">
         <v>7.99</v>
       </c>
-      <c r="W36" s="4" t="n">
+      <c r="Y36" s="4" t="n">
         <v>93.79000000000001</v>
       </c>
-      <c r="X36" s="4" t="n">
+      <c r="Z36" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="4" t="n">
+      <c r="AA36" s="4" t="inlineStr"/>
+      <c r="AB36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="4" t="n">
         <v>7.39</v>
       </c>
-      <c r="AA36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="4" t="inlineStr">
+      <c r="AD36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC36" s="4" t="inlineStr">
+      <c r="AF36" s="4" t="inlineStr">
         <is>
           <t>Momentum · News · Quality</t>
         </is>
       </c>
-      <c r="AD36" s="4" t="inlineStr"/>
-      <c r="AE36" s="4" t="inlineStr"/>
-      <c r="AF36" s="4" t="n">
+      <c r="AG36" s="4" t="inlineStr"/>
+      <c r="AH36" s="4" t="inlineStr"/>
+      <c r="AI36" s="4" t="n">
         <v>15.5</v>
       </c>
-      <c r="AG36" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ36" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -4691,94 +4908,103 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+16.4pp)</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="J37" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J37" s="4" t="n">
+      <c r="L37" s="4" t="n">
         <v>12.8</v>
       </c>
-      <c r="K37" s="4" t="n">
+      <c r="M37" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L37" s="4" t="n">
+      <c r="N37" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M37" s="4" t="n">
+      <c r="O37" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="P37" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="O37" s="4" t="n">
+      <c r="Q37" s="4" t="n">
         <v>159.84</v>
       </c>
-      <c r="P37" s="4" t="n">
+      <c r="R37" s="4" t="n">
         <v>159.84</v>
       </c>
-      <c r="Q37" s="4" t="n">
+      <c r="S37" s="4" t="n">
         <v>158.24</v>
       </c>
-      <c r="R37" s="4" t="n">
+      <c r="T37" s="4" t="n">
         <v>161.44</v>
       </c>
-      <c r="S37" s="4" t="n">
+      <c r="U37" s="4" t="n">
         <v>151.85</v>
       </c>
-      <c r="T37" s="4" t="n">
+      <c r="V37" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U37" s="4" t="n">
+      <c r="W37" s="4" t="n">
         <v>172.63</v>
       </c>
-      <c r="V37" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W37" s="4" t="n">
+      <c r="X37" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y37" s="4" t="n">
         <v>183.82</v>
       </c>
-      <c r="X37" s="4" t="n">
+      <c r="Z37" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" s="4" t="n">
+      <c r="AA37" s="4" t="inlineStr"/>
+      <c r="AB37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="4" t="n">
         <v>10.29</v>
       </c>
-      <c r="AA37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" s="4" t="inlineStr">
+      <c r="AD37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC37" s="4" t="inlineStr">
+      <c r="AF37" s="4" t="inlineStr">
         <is>
           <t>Momentum · News · Value</t>
         </is>
       </c>
-      <c r="AD37" s="4" t="inlineStr"/>
-      <c r="AE37" s="4" t="inlineStr"/>
-      <c r="AF37" s="4" t="n">
+      <c r="AG37" s="4" t="inlineStr"/>
+      <c r="AH37" s="4" t="inlineStr"/>
+      <c r="AI37" s="4" t="n">
         <v>16.4</v>
       </c>
-      <c r="AG37" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ37" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -4810,94 +5036,103 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+37.2pp)</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="J38" s="4" t="n">
         <v>28.7</v>
       </c>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J38" s="4" t="n">
+      <c r="L38" s="4" t="n">
         <v>-7.9</v>
       </c>
-      <c r="K38" s="4" t="n">
+      <c r="M38" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L38" s="4" t="n">
+      <c r="N38" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M38" s="4" t="n">
+      <c r="O38" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="P38" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O38" s="4" t="n">
+      <c r="Q38" s="4" t="n">
         <v>95.04000000000001</v>
       </c>
-      <c r="P38" s="4" t="n">
+      <c r="R38" s="4" t="n">
         <v>95.04000000000001</v>
       </c>
-      <c r="Q38" s="4" t="n">
+      <c r="S38" s="4" t="n">
         <v>94.09</v>
       </c>
-      <c r="R38" s="4" t="n">
+      <c r="T38" s="4" t="n">
         <v>95.98999999999999</v>
       </c>
-      <c r="S38" s="4" t="n">
+      <c r="U38" s="4" t="n">
         <v>90.29000000000001</v>
       </c>
-      <c r="T38" s="4" t="n">
+      <c r="V38" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U38" s="4" t="n">
+      <c r="W38" s="4" t="n">
         <v>102.64</v>
       </c>
-      <c r="V38" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W38" s="4" t="n">
+      <c r="X38" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y38" s="4" t="n">
         <v>109.3</v>
       </c>
-      <c r="X38" s="4" t="n">
+      <c r="Z38" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="4" t="n">
+      <c r="AA38" s="4" t="inlineStr"/>
+      <c r="AB38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="4" t="n">
         <v>-5.09</v>
       </c>
-      <c r="AB38" s="4" t="inlineStr">
+      <c r="AE38" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC38" s="4" t="inlineStr">
+      <c r="AF38" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AD38" s="4" t="inlineStr"/>
-      <c r="AE38" s="4" t="inlineStr"/>
-      <c r="AF38" s="4" t="n">
+      <c r="AG38" s="4" t="inlineStr"/>
+      <c r="AH38" s="4" t="inlineStr"/>
+      <c r="AI38" s="4" t="n">
         <v>37.17</v>
       </c>
-      <c r="AG38" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ38" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -4929,94 +5164,103 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+37.8pp)</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="J39" s="4" t="n">
         <v>30.8</v>
       </c>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J39" s="4" t="n">
+      <c r="L39" s="4" t="n">
         <v>-8.5</v>
       </c>
-      <c r="K39" s="4" t="n">
+      <c r="M39" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L39" s="4" t="n">
+      <c r="N39" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M39" s="4" t="n">
+      <c r="O39" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N39" s="4" t="inlineStr">
+      <c r="P39" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="O39" s="4" t="n">
+      <c r="Q39" s="4" t="n">
         <v>214.03</v>
       </c>
-      <c r="P39" s="4" t="n">
+      <c r="R39" s="4" t="n">
         <v>214.03</v>
       </c>
-      <c r="Q39" s="4" t="n">
+      <c r="S39" s="4" t="n">
         <v>211.89</v>
       </c>
-      <c r="R39" s="4" t="n">
+      <c r="T39" s="4" t="n">
         <v>216.17</v>
       </c>
-      <c r="S39" s="4" t="n">
+      <c r="U39" s="4" t="n">
         <v>203.33</v>
       </c>
-      <c r="T39" s="4" t="n">
+      <c r="V39" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U39" s="4" t="n">
+      <c r="W39" s="4" t="n">
         <v>231.15</v>
       </c>
-      <c r="V39" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W39" s="4" t="n">
+      <c r="X39" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y39" s="4" t="n">
         <v>246.13</v>
       </c>
-      <c r="X39" s="4" t="n">
+      <c r="Z39" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="4" t="n">
+      <c r="AA39" s="4" t="inlineStr"/>
+      <c r="AB39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="AA39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" s="4" t="inlineStr">
+      <c r="AD39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC39" s="4" t="inlineStr">
+      <c r="AF39" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AD39" s="4" t="inlineStr"/>
-      <c r="AE39" s="4" t="inlineStr"/>
-      <c r="AF39" s="4" t="n">
+      <c r="AG39" s="4" t="inlineStr"/>
+      <c r="AH39" s="4" t="inlineStr"/>
+      <c r="AI39" s="4" t="n">
         <v>37.79</v>
       </c>
-      <c r="AG39" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ39" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -5048,94 +5292,103 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+43.9pp)</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="H40" s="4" t="n">
+      <c r="J40" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J40" s="4" t="n">
+      <c r="L40" s="4" t="n">
         <v>-14.6</v>
       </c>
-      <c r="K40" s="4" t="n">
+      <c r="M40" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L40" s="4" t="n">
+      <c r="N40" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M40" s="4" t="n">
+      <c r="O40" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="P40" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O40" s="4" t="n">
+      <c r="Q40" s="4" t="n">
         <v>338.87</v>
       </c>
-      <c r="P40" s="4" t="n">
+      <c r="R40" s="4" t="n">
         <v>338.87</v>
       </c>
-      <c r="Q40" s="4" t="n">
+      <c r="S40" s="4" t="n">
         <v>335.48</v>
       </c>
-      <c r="R40" s="4" t="n">
+      <c r="T40" s="4" t="n">
         <v>342.26</v>
       </c>
-      <c r="S40" s="4" t="n">
+      <c r="U40" s="4" t="n">
         <v>321.93</v>
       </c>
-      <c r="T40" s="4" t="n">
+      <c r="V40" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U40" s="4" t="n">
+      <c r="W40" s="4" t="n">
         <v>365.98</v>
       </c>
-      <c r="V40" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W40" s="4" t="n">
+      <c r="X40" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y40" s="4" t="n">
         <v>389.7</v>
       </c>
-      <c r="X40" s="4" t="n">
+      <c r="Z40" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="4" t="n">
+      <c r="AA40" s="4" t="inlineStr"/>
+      <c r="AB40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="4" t="n">
         <v>-2.04</v>
       </c>
-      <c r="AB40" s="4" t="inlineStr">
+      <c r="AE40" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC40" s="4" t="inlineStr">
+      <c r="AF40" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AD40" s="4" t="inlineStr"/>
-      <c r="AE40" s="4" t="inlineStr"/>
-      <c r="AF40" s="4" t="n">
+      <c r="AG40" s="4" t="inlineStr"/>
+      <c r="AH40" s="4" t="inlineStr"/>
+      <c r="AI40" s="4" t="n">
         <v>43.85</v>
       </c>
-      <c r="AG40" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ40" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -5167,94 +5420,103 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+45.6pp)</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="J41" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J41" s="4" t="n">
+      <c r="L41" s="4" t="n">
         <v>-16.4</v>
       </c>
-      <c r="K41" s="4" t="n">
+      <c r="M41" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L41" s="4" t="n">
+      <c r="N41" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M41" s="4" t="n">
+      <c r="O41" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N41" s="4" t="inlineStr">
+      <c r="P41" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O41" s="4" t="n">
+      <c r="Q41" s="4" t="n">
         <v>97.67</v>
       </c>
-      <c r="P41" s="4" t="n">
+      <c r="R41" s="4" t="n">
         <v>97.67</v>
       </c>
-      <c r="Q41" s="4" t="n">
+      <c r="S41" s="4" t="n">
         <v>96.69</v>
       </c>
-      <c r="R41" s="4" t="n">
+      <c r="T41" s="4" t="n">
         <v>98.65000000000001</v>
       </c>
-      <c r="S41" s="4" t="n">
+      <c r="U41" s="4" t="n">
         <v>92.79000000000001</v>
       </c>
-      <c r="T41" s="4" t="n">
+      <c r="V41" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U41" s="4" t="n">
+      <c r="W41" s="4" t="n">
         <v>105.48</v>
       </c>
-      <c r="V41" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W41" s="4" t="n">
+      <c r="X41" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y41" s="4" t="n">
         <v>112.32</v>
       </c>
-      <c r="X41" s="4" t="n">
+      <c r="Z41" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="4" t="n">
+      <c r="AA41" s="4" t="inlineStr"/>
+      <c r="AB41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="4" t="n">
         <v>-1.52</v>
       </c>
-      <c r="AB41" s="4" t="inlineStr">
+      <c r="AE41" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC41" s="4" t="inlineStr">
+      <c r="AF41" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AD41" s="4" t="inlineStr"/>
-      <c r="AE41" s="4" t="inlineStr"/>
-      <c r="AF41" s="4" t="n">
+      <c r="AG41" s="4" t="inlineStr"/>
+      <c r="AH41" s="4" t="inlineStr"/>
+      <c r="AI41" s="4" t="n">
         <v>45.62</v>
       </c>
-      <c r="AG41" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ41" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -5286,99 +5548,108 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+45.9pp)</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="J42" s="4" t="n">
         <v>28.3</v>
       </c>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="K42" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J42" s="4" t="n">
+      <c r="L42" s="4" t="n">
         <v>-16.7</v>
       </c>
-      <c r="K42" s="4" t="n">
+      <c r="M42" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L42" s="4" t="n">
+      <c r="N42" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M42" s="4" t="n">
+      <c r="O42" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="P42" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O42" s="4" t="n">
+      <c r="Q42" s="4" t="n">
         <v>267.71</v>
       </c>
-      <c r="P42" s="4" t="n">
+      <c r="R42" s="4" t="n">
         <v>267.71</v>
       </c>
-      <c r="Q42" s="4" t="n">
+      <c r="S42" s="4" t="n">
         <v>265.03</v>
       </c>
-      <c r="R42" s="4" t="n">
+      <c r="T42" s="4" t="n">
         <v>270.39</v>
       </c>
-      <c r="S42" s="4" t="n">
+      <c r="U42" s="4" t="n">
         <v>254.32</v>
       </c>
-      <c r="T42" s="4" t="n">
+      <c r="V42" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U42" s="4" t="n">
+      <c r="W42" s="4" t="n">
         <v>289.13</v>
       </c>
-      <c r="V42" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W42" s="4" t="n">
+      <c r="X42" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y42" s="4" t="n">
         <v>307.87</v>
       </c>
-      <c r="X42" s="4" t="n">
+      <c r="Z42" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="4" t="n">
+      <c r="AA42" s="4" t="inlineStr"/>
+      <c r="AB42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="AA42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="4" t="inlineStr">
+      <c r="AD42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC42" s="4" t="inlineStr">
+      <c r="AF42" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AD42" s="4" t="inlineStr"/>
-      <c r="AE42" s="4" t="inlineStr"/>
-      <c r="AF42" s="4" t="n">
+      <c r="AG42" s="4" t="inlineStr"/>
+      <c r="AH42" s="4" t="inlineStr"/>
+      <c r="AI42" s="4" t="n">
         <v>45.94</v>
       </c>
-      <c r="AG42" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ42" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG42"/>
+  <autoFilter ref="A1:AJ42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_daily_2026-08-01.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-01.xlsx
@@ -810,7 +810,7 @@
       </c>
       <c r="AJ2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AJ3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="AJ4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="AJ5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="AJ6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="AJ7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AJ8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AJ9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="AJ10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AJ11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="AJ12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="AJ13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="AJ14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="AJ15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AJ16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2499,9 @@
       </c>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="J17" s="4" t="n">
         <v>83</v>
       </c>
@@ -2578,7 +2580,7 @@
       </c>
       <c r="AJ17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2617,9 @@
       </c>
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="J18" s="4" t="n">
         <v>89</v>
       </c>
@@ -2694,7 +2698,7 @@
       </c>
       <c r="AJ18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2735,9 @@
       </c>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="J19" s="4" t="n">
         <v>72</v>
       </c>
@@ -2810,7 +2816,7 @@
       </c>
       <c r="AJ19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2853,9 @@
       </c>
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="J20" s="4" t="n">
         <v>86</v>
       </c>
@@ -2926,7 +2934,7 @@
       </c>
       <c r="AJ20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2971,9 @@
       </c>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="J21" s="4" t="n">
         <v>72</v>
       </c>
@@ -3042,7 +3052,7 @@
       </c>
       <c r="AJ21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3089,9 @@
       </c>
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J22" s="4" t="n">
         <v>72</v>
       </c>
@@ -3158,7 +3170,7 @@
       </c>
       <c r="AJ22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3207,9 @@
       </c>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="n">
+        <v>7</v>
+      </c>
       <c r="J23" s="4" t="n">
         <v>69</v>
       </c>
@@ -3274,7 +3288,7 @@
       </c>
       <c r="AJ23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3325,9 @@
       </c>
       <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="J24" s="4" t="n">
         <v>67</v>
       </c>
@@ -3390,7 +3406,7 @@
       </c>
       <c r="AJ24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3443,9 @@
       </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr"/>
-      <c r="I25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="n">
+        <v>9</v>
+      </c>
       <c r="J25" s="4" t="n">
         <v>64</v>
       </c>
@@ -3506,7 +3524,7 @@
       </c>
       <c r="AJ25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3561,9 @@
       </c>
       <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="4" t="inlineStr"/>
+      <c r="I26" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="J26" s="4" t="n">
         <v>66</v>
       </c>
@@ -3622,7 +3642,7 @@
       </c>
       <c r="AJ26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3675,9 @@
       </c>
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="n">
+        <v>11</v>
+      </c>
       <c r="J27" s="4" t="n">
         <v>66</v>
       </c>
@@ -3734,7 +3756,7 @@
       </c>
       <c r="AJ27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3880,7 @@
       </c>
       <c r="AJ28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -3980,7 +4002,7 @@
       </c>
       <c r="AJ29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4130,7 @@
       </c>
       <c r="AJ30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4258,7 @@
       </c>
       <c r="AJ31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4386,7 @@
       </c>
       <c r="AJ32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4514,7 @@
       </c>
       <c r="AJ33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4642,7 @@
       </c>
       <c r="AJ34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4770,7 @@
       </c>
       <c r="AJ35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4898,7 @@
       </c>
       <c r="AJ36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5026,7 @@
       </c>
       <c r="AJ37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5154,7 @@
       </c>
       <c r="AJ38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5282,7 @@
       </c>
       <c r="AJ39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5410,7 @@
       </c>
       <c r="AJ40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5538,7 @@
       </c>
       <c r="AJ41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5666,7 @@
       </c>
       <c r="AJ42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:18</t>
+          <t>2026-08-01 23:12</t>
         </is>
       </c>
     </row>
